--- a/Data/EXCEL/Transfer/salemon/202208/2325-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/2325-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3517E76-8475-444E-8E51-CB11B5522F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E79DECE7-1B39-4A2F-ABC4-0582344F98B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="2325-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -848,22 +856,22 @@
     <xf numFmtId="3" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1221,17 +1229,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q191"/>
+  <dimension ref="A1:Q192"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="7" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
+    <col min="10" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="14" width="13.625" customWidth="1"/>
+    <col min="15" max="16" width="14.25" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,7 +1392,7 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>17</v>
@@ -1405,39 +1413,39 @@
         <v>17</v>
       </c>
       <c r="H5" s="8">
-        <v>118.7</v>
+        <v>115.5</v>
       </c>
       <c r="I5" s="9">
-        <v>-1.45</v>
+        <v>-2.72</v>
       </c>
       <c r="J5" s="10">
-        <v>23.7</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="K5" s="8">
-        <v>754.5</v>
+        <v>870</v>
       </c>
       <c r="L5" s="10">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
       <c r="M5" s="8">
-        <v>118.7</v>
+        <v>115.5</v>
       </c>
       <c r="N5" s="9">
-        <v>-1.45</v>
+        <v>-2.72</v>
       </c>
       <c r="O5" s="10">
-        <v>23.7</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="P5" s="8">
-        <v>754.5</v>
+        <v>870</v>
       </c>
       <c r="Q5" s="10">
-        <v>25.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>17</v>
@@ -1458,39 +1466,39 @@
         <v>17</v>
       </c>
       <c r="H6" s="8">
-        <v>120.5</v>
-      </c>
-      <c r="I6" s="10">
-        <v>7.93</v>
+        <v>118.7</v>
+      </c>
+      <c r="I6" s="9">
+        <v>-1.45</v>
       </c>
       <c r="J6" s="10">
-        <v>36</v>
+        <v>23.7</v>
       </c>
       <c r="K6" s="8">
-        <v>635.79999999999995</v>
+        <v>754.5</v>
       </c>
       <c r="L6" s="10">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="M6" s="8">
-        <v>120.5</v>
-      </c>
-      <c r="N6" s="10">
-        <v>7.93</v>
+        <v>118.7</v>
+      </c>
+      <c r="N6" s="9">
+        <v>-1.45</v>
       </c>
       <c r="O6" s="10">
-        <v>36</v>
+        <v>23.7</v>
       </c>
       <c r="P6" s="8">
-        <v>635.79999999999995</v>
+        <v>754.5</v>
       </c>
       <c r="Q6" s="10">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>17</v>
@@ -1511,39 +1519,39 @@
         <v>17</v>
       </c>
       <c r="H7" s="8">
-        <v>111.6</v>
+        <v>120.5</v>
       </c>
       <c r="I7" s="10">
-        <v>3.69</v>
+        <v>7.93</v>
       </c>
       <c r="J7" s="10">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K7" s="8">
-        <v>515.29999999999995</v>
+        <v>635.79999999999995</v>
       </c>
       <c r="L7" s="10">
-        <v>24.2</v>
+        <v>26.3</v>
       </c>
       <c r="M7" s="8">
-        <v>111.6</v>
+        <v>120.5</v>
       </c>
       <c r="N7" s="10">
-        <v>3.69</v>
+        <v>7.93</v>
       </c>
       <c r="O7" s="10">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="P7" s="8">
-        <v>515.29999999999995</v>
+        <v>635.79999999999995</v>
       </c>
       <c r="Q7" s="10">
-        <v>24.2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>17</v>
@@ -1564,39 +1572,39 @@
         <v>17</v>
       </c>
       <c r="H8" s="8">
-        <v>107.6</v>
-      </c>
-      <c r="I8" s="9">
-        <v>-2.7</v>
+        <v>111.6</v>
+      </c>
+      <c r="I8" s="10">
+        <v>3.69</v>
       </c>
       <c r="J8" s="10">
-        <v>32.299999999999997</v>
+        <v>26</v>
       </c>
       <c r="K8" s="8">
-        <v>403.7</v>
+        <v>515.29999999999995</v>
       </c>
       <c r="L8" s="10">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="M8" s="8">
-        <v>107.6</v>
-      </c>
-      <c r="N8" s="9">
-        <v>-2.7</v>
+        <v>111.6</v>
+      </c>
+      <c r="N8" s="10">
+        <v>3.69</v>
       </c>
       <c r="O8" s="10">
-        <v>32.299999999999997</v>
+        <v>26</v>
       </c>
       <c r="P8" s="8">
-        <v>403.7</v>
+        <v>515.29999999999995</v>
       </c>
       <c r="Q8" s="10">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>17</v>
@@ -1617,39 +1625,39 @@
         <v>17</v>
       </c>
       <c r="H9" s="8">
-        <v>110.6</v>
-      </c>
-      <c r="I9" s="10">
-        <v>20.6</v>
+        <v>107.6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>-2.7</v>
       </c>
       <c r="J9" s="10">
-        <v>30.8</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="K9" s="8">
-        <v>296.10000000000002</v>
+        <v>403.7</v>
       </c>
       <c r="L9" s="10">
-        <v>21</v>
+        <v>23.8</v>
       </c>
       <c r="M9" s="8">
-        <v>110.6</v>
-      </c>
-      <c r="N9" s="10">
-        <v>20.6</v>
+        <v>107.6</v>
+      </c>
+      <c r="N9" s="9">
+        <v>-2.7</v>
       </c>
       <c r="O9" s="10">
-        <v>30.8</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="P9" s="8">
-        <v>296.10000000000002</v>
+        <v>403.7</v>
       </c>
       <c r="Q9" s="10">
-        <v>21</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>17</v>
@@ -1670,39 +1678,39 @@
         <v>17</v>
       </c>
       <c r="H10" s="8">
-        <v>91.71</v>
-      </c>
-      <c r="I10" s="9">
-        <v>-2.2000000000000002</v>
+        <v>110.6</v>
+      </c>
+      <c r="I10" s="10">
+        <v>20.6</v>
       </c>
       <c r="J10" s="10">
-        <v>16.5</v>
+        <v>30.8</v>
       </c>
       <c r="K10" s="8">
-        <v>185.5</v>
+        <v>296.10000000000002</v>
       </c>
       <c r="L10" s="10">
-        <v>15.8</v>
+        <v>21</v>
       </c>
       <c r="M10" s="8">
-        <v>91.71</v>
-      </c>
-      <c r="N10" s="9">
-        <v>-2.2000000000000002</v>
+        <v>110.6</v>
+      </c>
+      <c r="N10" s="10">
+        <v>20.6</v>
       </c>
       <c r="O10" s="10">
-        <v>16.5</v>
+        <v>30.8</v>
       </c>
       <c r="P10" s="8">
-        <v>185.5</v>
+        <v>296.10000000000002</v>
       </c>
       <c r="Q10" s="10">
-        <v>15.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1723,39 +1731,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="8">
-        <v>93.78</v>
+        <v>91.71</v>
       </c>
       <c r="I11" s="9">
-        <v>-3.19</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="J11" s="10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="K11" s="8">
-        <v>93.78</v>
+        <v>185.5</v>
       </c>
       <c r="L11" s="10">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="M11" s="8">
-        <v>93.78</v>
+        <v>91.71</v>
       </c>
       <c r="N11" s="9">
-        <v>-3.19</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="O11" s="10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="P11" s="8">
-        <v>93.78</v>
+        <v>185.5</v>
       </c>
       <c r="Q11" s="10">
-        <v>15</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1776,39 +1784,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="8">
-        <v>96.87</v>
-      </c>
-      <c r="I12" s="10">
-        <v>1.25</v>
+        <v>93.78</v>
+      </c>
+      <c r="I12" s="9">
+        <v>-3.19</v>
       </c>
       <c r="J12" s="10">
-        <v>11.9</v>
-      </c>
-      <c r="K12" s="11">
-        <v>1078</v>
+        <v>15</v>
+      </c>
+      <c r="K12" s="8">
+        <v>93.78</v>
       </c>
       <c r="L12" s="10">
-        <v>5.68</v>
+        <v>15</v>
       </c>
       <c r="M12" s="8">
-        <v>96.87</v>
-      </c>
-      <c r="N12" s="10">
-        <v>1.25</v>
+        <v>93.78</v>
+      </c>
+      <c r="N12" s="9">
+        <v>-3.19</v>
       </c>
       <c r="O12" s="10">
-        <v>11.9</v>
-      </c>
-      <c r="P12" s="11">
-        <v>1078</v>
+        <v>15</v>
+      </c>
+      <c r="P12" s="8">
+        <v>93.78</v>
       </c>
       <c r="Q12" s="10">
-        <v>5.68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1829,39 +1837,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="8">
-        <v>95.67</v>
+        <v>96.87</v>
       </c>
       <c r="I13" s="10">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="J13" s="10">
-        <v>16</v>
-      </c>
-      <c r="K13" s="8">
-        <v>981.5</v>
+        <v>11.9</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1078</v>
       </c>
       <c r="L13" s="10">
-        <v>5.1100000000000003</v>
+        <v>5.68</v>
       </c>
       <c r="M13" s="8">
-        <v>95.67</v>
+        <v>96.87</v>
       </c>
       <c r="N13" s="10">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="O13" s="10">
-        <v>16</v>
-      </c>
-      <c r="P13" s="8">
-        <v>981.5</v>
+        <v>11.9</v>
+      </c>
+      <c r="P13" s="11">
+        <v>1078</v>
       </c>
       <c r="Q13" s="10">
-        <v>5.1100000000000003</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1882,39 +1890,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="8">
-        <v>94.01</v>
-      </c>
-      <c r="I14" s="9">
-        <v>-1.06</v>
+        <v>95.67</v>
+      </c>
+      <c r="I14" s="10">
+        <v>1.76</v>
       </c>
       <c r="J14" s="10">
-        <v>27.6</v>
+        <v>16</v>
       </c>
       <c r="K14" s="8">
-        <v>885.8</v>
+        <v>981.5</v>
       </c>
       <c r="L14" s="10">
-        <v>4.05</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="M14" s="8">
-        <v>94.01</v>
-      </c>
-      <c r="N14" s="9">
-        <v>-1.06</v>
+        <v>95.67</v>
+      </c>
+      <c r="N14" s="10">
+        <v>1.76</v>
       </c>
       <c r="O14" s="10">
-        <v>27.6</v>
+        <v>16</v>
       </c>
       <c r="P14" s="8">
-        <v>885.8</v>
+        <v>981.5</v>
       </c>
       <c r="Q14" s="10">
-        <v>4.05</v>
+        <v>5.1100000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1935,39 +1943,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="8">
-        <v>95.03</v>
+        <v>94.01</v>
       </c>
       <c r="I15" s="9">
-        <v>-2.56</v>
+        <v>-1.06</v>
       </c>
       <c r="J15" s="10">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="K15" s="8">
-        <v>791.8</v>
+        <v>885.8</v>
       </c>
       <c r="L15" s="10">
-        <v>1.82</v>
+        <v>4.05</v>
       </c>
       <c r="M15" s="8">
-        <v>95.03</v>
+        <v>94.01</v>
       </c>
       <c r="N15" s="9">
-        <v>-2.56</v>
+        <v>-1.06</v>
       </c>
       <c r="O15" s="10">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="P15" s="8">
-        <v>791.8</v>
+        <v>885.8</v>
       </c>
       <c r="Q15" s="10">
-        <v>1.82</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1988,39 +1996,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="8">
-        <v>97.53</v>
-      </c>
-      <c r="I16" s="10">
-        <v>1.64</v>
+        <v>95.03</v>
+      </c>
+      <c r="I16" s="9">
+        <v>-2.56</v>
       </c>
       <c r="J16" s="10">
-        <v>2.99</v>
+        <v>28.5</v>
       </c>
       <c r="K16" s="8">
-        <v>696.8</v>
-      </c>
-      <c r="L16" s="9">
-        <v>-0.98</v>
+        <v>791.8</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1.82</v>
       </c>
       <c r="M16" s="8">
-        <v>97.53</v>
-      </c>
-      <c r="N16" s="10">
-        <v>1.64</v>
+        <v>95.03</v>
+      </c>
+      <c r="N16" s="9">
+        <v>-2.56</v>
       </c>
       <c r="O16" s="10">
-        <v>2.99</v>
+        <v>28.5</v>
       </c>
       <c r="P16" s="8">
-        <v>696.8</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>-0.98</v>
+        <v>791.8</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1.82</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2041,39 +2049,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="8">
-        <v>95.95</v>
+        <v>97.53</v>
       </c>
       <c r="I17" s="10">
-        <v>8.31</v>
+        <v>1.64</v>
       </c>
       <c r="J17" s="10">
-        <v>2.13</v>
+        <v>2.99</v>
       </c>
       <c r="K17" s="8">
-        <v>599.29999999999995</v>
+        <v>696.8</v>
       </c>
       <c r="L17" s="9">
-        <v>-1.59</v>
+        <v>-0.98</v>
       </c>
       <c r="M17" s="8">
-        <v>95.95</v>
+        <v>97.53</v>
       </c>
       <c r="N17" s="10">
-        <v>8.31</v>
+        <v>1.64</v>
       </c>
       <c r="O17" s="10">
-        <v>2.13</v>
+        <v>2.99</v>
       </c>
       <c r="P17" s="8">
-        <v>599.29999999999995</v>
+        <v>696.8</v>
       </c>
       <c r="Q17" s="9">
-        <v>-1.59</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2094,39 +2102,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="8">
-        <v>88.59</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>-4.75</v>
+        <v>95.95</v>
+      </c>
+      <c r="I18" s="10">
+        <v>8.31</v>
+      </c>
+      <c r="J18" s="10">
+        <v>2.13</v>
       </c>
       <c r="K18" s="8">
-        <v>503.3</v>
+        <v>599.29999999999995</v>
       </c>
       <c r="L18" s="9">
-        <v>-2.27</v>
+        <v>-1.59</v>
       </c>
       <c r="M18" s="8">
-        <v>88.59</v>
-      </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
-        <v>-4.75</v>
+        <v>95.95</v>
+      </c>
+      <c r="N18" s="10">
+        <v>8.31</v>
+      </c>
+      <c r="O18" s="10">
+        <v>2.13</v>
       </c>
       <c r="P18" s="8">
-        <v>503.3</v>
+        <v>599.29999999999995</v>
       </c>
       <c r="Q18" s="9">
-        <v>-2.27</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2149,37 +2157,37 @@
       <c r="H19" s="8">
         <v>88.59</v>
       </c>
-      <c r="I19" s="10">
-        <v>8.9</v>
+      <c r="I19" s="8">
+        <v>0</v>
       </c>
       <c r="J19" s="9">
-        <v>-1.85</v>
+        <v>-4.75</v>
       </c>
       <c r="K19" s="8">
-        <v>414.7</v>
+        <v>503.3</v>
       </c>
       <c r="L19" s="9">
-        <v>-1.73</v>
+        <v>-2.27</v>
       </c>
       <c r="M19" s="8">
         <v>88.59</v>
       </c>
-      <c r="N19" s="10">
-        <v>8.9</v>
+      <c r="N19" s="8">
+        <v>0</v>
       </c>
       <c r="O19" s="9">
-        <v>-1.85</v>
+        <v>-4.75</v>
       </c>
       <c r="P19" s="8">
-        <v>414.7</v>
+        <v>503.3</v>
       </c>
       <c r="Q19" s="9">
-        <v>-1.73</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2200,39 +2208,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="8">
-        <v>81.34</v>
-      </c>
-      <c r="I20" s="9">
-        <v>-3.8</v>
+        <v>88.59</v>
+      </c>
+      <c r="I20" s="10">
+        <v>8.9</v>
       </c>
       <c r="J20" s="9">
-        <v>-8.34</v>
+        <v>-1.85</v>
       </c>
       <c r="K20" s="8">
-        <v>326.10000000000002</v>
+        <v>414.7</v>
       </c>
       <c r="L20" s="9">
-        <v>-1.7</v>
+        <v>-1.73</v>
       </c>
       <c r="M20" s="8">
-        <v>81.34</v>
-      </c>
-      <c r="N20" s="9">
-        <v>-3.8</v>
+        <v>88.59</v>
+      </c>
+      <c r="N20" s="10">
+        <v>8.9</v>
       </c>
       <c r="O20" s="9">
-        <v>-8.34</v>
+        <v>-1.85</v>
       </c>
       <c r="P20" s="8">
-        <v>326.10000000000002</v>
+        <v>414.7</v>
       </c>
       <c r="Q20" s="9">
-        <v>-1.7</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2253,39 +2261,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="8">
-        <v>84.56</v>
-      </c>
-      <c r="I21" s="10">
-        <v>7.46</v>
+        <v>81.34</v>
+      </c>
+      <c r="I21" s="9">
+        <v>-3.8</v>
       </c>
       <c r="J21" s="9">
-        <v>-1.1100000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="K21" s="8">
-        <v>244.8</v>
-      </c>
-      <c r="L21" s="10">
-        <v>0.72</v>
+        <v>326.10000000000002</v>
+      </c>
+      <c r="L21" s="9">
+        <v>-1.7</v>
       </c>
       <c r="M21" s="8">
-        <v>84.56</v>
-      </c>
-      <c r="N21" s="10">
-        <v>7.46</v>
+        <v>81.34</v>
+      </c>
+      <c r="N21" s="9">
+        <v>-3.8</v>
       </c>
       <c r="O21" s="9">
-        <v>-1.1100000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="P21" s="8">
-        <v>244.8</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>0.72</v>
+        <v>326.10000000000002</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2306,39 +2314,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="8">
-        <v>78.69</v>
-      </c>
-      <c r="I22" s="9">
-        <v>-3.49</v>
-      </c>
-      <c r="J22" s="10">
-        <v>0.7</v>
+        <v>84.56</v>
+      </c>
+      <c r="I22" s="10">
+        <v>7.46</v>
+      </c>
+      <c r="J22" s="9">
+        <v>-1.1100000000000001</v>
       </c>
       <c r="K22" s="8">
-        <v>160.19999999999999</v>
+        <v>244.8</v>
       </c>
       <c r="L22" s="10">
-        <v>1.71</v>
+        <v>0.72</v>
       </c>
       <c r="M22" s="8">
-        <v>78.69</v>
-      </c>
-      <c r="N22" s="9">
-        <v>-3.49</v>
-      </c>
-      <c r="O22" s="10">
-        <v>0.7</v>
+        <v>84.56</v>
+      </c>
+      <c r="N22" s="10">
+        <v>7.46</v>
+      </c>
+      <c r="O22" s="9">
+        <v>-1.1100000000000001</v>
       </c>
       <c r="P22" s="8">
-        <v>160.19999999999999</v>
+        <v>244.8</v>
       </c>
       <c r="Q22" s="10">
-        <v>1.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2359,39 +2367,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="8">
-        <v>81.540000000000006</v>
+        <v>78.69</v>
       </c>
       <c r="I23" s="9">
-        <v>-5.81</v>
+        <v>-3.49</v>
       </c>
       <c r="J23" s="10">
-        <v>2.71</v>
+        <v>0.7</v>
       </c>
       <c r="K23" s="8">
-        <v>81.540000000000006</v>
+        <v>160.19999999999999</v>
       </c>
       <c r="L23" s="10">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
       <c r="M23" s="8">
-        <v>81.540000000000006</v>
+        <v>78.69</v>
       </c>
       <c r="N23" s="9">
-        <v>-5.81</v>
+        <v>-3.49</v>
       </c>
       <c r="O23" s="10">
-        <v>2.71</v>
+        <v>0.7</v>
       </c>
       <c r="P23" s="8">
-        <v>81.540000000000006</v>
+        <v>160.19999999999999</v>
       </c>
       <c r="Q23" s="10">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2412,39 +2420,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="8">
-        <v>86.58</v>
-      </c>
-      <c r="I24" s="10">
-        <v>5.01</v>
+        <v>81.540000000000006</v>
+      </c>
+      <c r="I24" s="9">
+        <v>-5.81</v>
       </c>
       <c r="J24" s="10">
-        <v>0.71</v>
-      </c>
-      <c r="K24" s="11">
-        <v>1020</v>
+        <v>2.71</v>
+      </c>
+      <c r="K24" s="8">
+        <v>81.540000000000006</v>
       </c>
       <c r="L24" s="10">
-        <v>14.7</v>
+        <v>2.71</v>
       </c>
       <c r="M24" s="8">
-        <v>86.58</v>
-      </c>
-      <c r="N24" s="10">
-        <v>5.01</v>
+        <v>81.540000000000006</v>
+      </c>
+      <c r="N24" s="9">
+        <v>-5.81</v>
       </c>
       <c r="O24" s="10">
-        <v>0.71</v>
-      </c>
-      <c r="P24" s="11">
-        <v>1020</v>
+        <v>2.71</v>
+      </c>
+      <c r="P24" s="8">
+        <v>81.540000000000006</v>
       </c>
       <c r="Q24" s="10">
-        <v>14.7</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2465,39 +2473,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="8">
-        <v>82.44</v>
+        <v>86.58</v>
       </c>
       <c r="I25" s="10">
-        <v>11.9</v>
-      </c>
-      <c r="J25" s="9">
-        <v>-2.75</v>
-      </c>
-      <c r="K25" s="8">
-        <v>933.8</v>
+        <v>5.01</v>
+      </c>
+      <c r="J25" s="10">
+        <v>0.71</v>
+      </c>
+      <c r="K25" s="11">
+        <v>1020</v>
       </c>
       <c r="L25" s="10">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
       <c r="M25" s="8">
-        <v>82.44</v>
+        <v>86.58</v>
       </c>
       <c r="N25" s="10">
-        <v>11.9</v>
-      </c>
-      <c r="O25" s="9">
-        <v>-2.75</v>
-      </c>
-      <c r="P25" s="8">
-        <v>933.8</v>
+        <v>5.01</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0.71</v>
+      </c>
+      <c r="P25" s="11">
+        <v>1020</v>
       </c>
       <c r="Q25" s="10">
-        <v>16.2</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2518,39 +2526,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="8">
-        <v>73.67</v>
-      </c>
-      <c r="I26" s="9">
-        <v>-0.39</v>
+        <v>82.44</v>
+      </c>
+      <c r="I26" s="10">
+        <v>11.9</v>
       </c>
       <c r="J26" s="9">
-        <v>-10.5</v>
+        <v>-2.75</v>
       </c>
       <c r="K26" s="8">
-        <v>851.3</v>
+        <v>933.8</v>
       </c>
       <c r="L26" s="10">
-        <v>18.399999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="M26" s="8">
-        <v>73.67</v>
-      </c>
-      <c r="N26" s="9">
-        <v>-0.39</v>
+        <v>82.44</v>
+      </c>
+      <c r="N26" s="10">
+        <v>11.9</v>
       </c>
       <c r="O26" s="9">
-        <v>-10.5</v>
+        <v>-2.75</v>
       </c>
       <c r="P26" s="8">
-        <v>851.3</v>
+        <v>933.8</v>
       </c>
       <c r="Q26" s="10">
-        <v>18.399999999999999</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2571,39 +2579,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="8">
-        <v>73.959999999999994</v>
+        <v>73.67</v>
       </c>
       <c r="I27" s="9">
-        <v>-21.9</v>
+        <v>-0.39</v>
       </c>
       <c r="J27" s="9">
-        <v>-10.6</v>
+        <v>-10.5</v>
       </c>
       <c r="K27" s="8">
-        <v>777.7</v>
+        <v>851.3</v>
       </c>
       <c r="L27" s="10">
-        <v>22.1</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="M27" s="8">
-        <v>73.959999999999994</v>
+        <v>73.67</v>
       </c>
       <c r="N27" s="9">
-        <v>-21.9</v>
+        <v>-0.39</v>
       </c>
       <c r="O27" s="9">
-        <v>-10.6</v>
+        <v>-10.5</v>
       </c>
       <c r="P27" s="8">
-        <v>777.7</v>
+        <v>851.3</v>
       </c>
       <c r="Q27" s="10">
-        <v>22.1</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2624,39 +2632,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="8">
-        <v>94.7</v>
-      </c>
-      <c r="I28" s="10">
-        <v>0.79</v>
-      </c>
-      <c r="J28" s="10">
-        <v>19.5</v>
+        <v>73.959999999999994</v>
+      </c>
+      <c r="I28" s="9">
+        <v>-21.9</v>
+      </c>
+      <c r="J28" s="9">
+        <v>-10.6</v>
       </c>
       <c r="K28" s="8">
-        <v>703.7</v>
+        <v>777.7</v>
       </c>
       <c r="L28" s="10">
-        <v>27</v>
+        <v>22.1</v>
       </c>
       <c r="M28" s="8">
-        <v>94.7</v>
-      </c>
-      <c r="N28" s="10">
-        <v>0.79</v>
-      </c>
-      <c r="O28" s="10">
-        <v>19.5</v>
+        <v>73.959999999999994</v>
+      </c>
+      <c r="N28" s="9">
+        <v>-21.9</v>
+      </c>
+      <c r="O28" s="9">
+        <v>-10.6</v>
       </c>
       <c r="P28" s="8">
-        <v>703.7</v>
+        <v>777.7</v>
       </c>
       <c r="Q28" s="10">
-        <v>27</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2677,39 +2685,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="8">
-        <v>93.95</v>
+        <v>94.7</v>
       </c>
       <c r="I29" s="10">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="J29" s="10">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="K29" s="8">
-        <v>609</v>
+        <v>703.7</v>
       </c>
       <c r="L29" s="10">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="M29" s="8">
-        <v>93.95</v>
+        <v>94.7</v>
       </c>
       <c r="N29" s="10">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="O29" s="10">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="P29" s="8">
-        <v>609</v>
+        <v>703.7</v>
       </c>
       <c r="Q29" s="10">
-        <v>28.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2730,39 +2738,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="8">
-        <v>93.01</v>
+        <v>93.95</v>
       </c>
       <c r="I30" s="10">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="J30" s="10">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="K30" s="8">
-        <v>515.1</v>
+        <v>609</v>
       </c>
       <c r="L30" s="10">
-        <v>29.4</v>
+        <v>28.2</v>
       </c>
       <c r="M30" s="8">
-        <v>93.01</v>
+        <v>93.95</v>
       </c>
       <c r="N30" s="10">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O30" s="10">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="P30" s="8">
-        <v>515.1</v>
+        <v>609</v>
       </c>
       <c r="Q30" s="10">
-        <v>29.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2783,39 +2791,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="8">
-        <v>90.26</v>
+        <v>93.01</v>
       </c>
       <c r="I31" s="10">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="J31" s="10">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="K31" s="8">
-        <v>422</v>
+        <v>515.1</v>
       </c>
       <c r="L31" s="10">
-        <v>30.4</v>
+        <v>29.4</v>
       </c>
       <c r="M31" s="8">
-        <v>90.26</v>
+        <v>93.01</v>
       </c>
       <c r="N31" s="10">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="O31" s="10">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="P31" s="8">
-        <v>422</v>
+        <v>515.1</v>
       </c>
       <c r="Q31" s="10">
-        <v>30.4</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2836,39 +2844,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="8">
-        <v>88.75</v>
+        <v>90.26</v>
       </c>
       <c r="I32" s="10">
-        <v>3.78</v>
+        <v>1.7</v>
       </c>
       <c r="J32" s="10">
-        <v>32.799999999999997</v>
+        <v>24.8</v>
       </c>
       <c r="K32" s="8">
-        <v>331.8</v>
+        <v>422</v>
       </c>
       <c r="L32" s="10">
-        <v>32</v>
+        <v>30.4</v>
       </c>
       <c r="M32" s="8">
-        <v>88.75</v>
+        <v>90.26</v>
       </c>
       <c r="N32" s="10">
-        <v>3.78</v>
+        <v>1.7</v>
       </c>
       <c r="O32" s="10">
-        <v>32.799999999999997</v>
+        <v>24.8</v>
       </c>
       <c r="P32" s="8">
-        <v>331.8</v>
+        <v>422</v>
       </c>
       <c r="Q32" s="10">
-        <v>32</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2889,39 +2897,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="8">
-        <v>85.51</v>
+        <v>88.75</v>
       </c>
       <c r="I33" s="10">
-        <v>9.43</v>
+        <v>3.78</v>
       </c>
       <c r="J33" s="10">
-        <v>33.4</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="K33" s="8">
-        <v>243</v>
+        <v>331.8</v>
       </c>
       <c r="L33" s="10">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="M33" s="8">
-        <v>85.51</v>
+        <v>88.75</v>
       </c>
       <c r="N33" s="10">
-        <v>9.43</v>
+        <v>3.78</v>
       </c>
       <c r="O33" s="10">
-        <v>33.4</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="P33" s="8">
-        <v>243</v>
+        <v>331.8</v>
       </c>
       <c r="Q33" s="10">
-        <v>31.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2942,39 +2950,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="8">
-        <v>78.14</v>
-      </c>
-      <c r="I34" s="9">
-        <v>-1.57</v>
+        <v>85.51</v>
+      </c>
+      <c r="I34" s="10">
+        <v>9.43</v>
       </c>
       <c r="J34" s="10">
-        <v>37</v>
+        <v>33.4</v>
       </c>
       <c r="K34" s="8">
-        <v>157.5</v>
+        <v>243</v>
       </c>
       <c r="L34" s="10">
-        <v>30.8</v>
+        <v>31.7</v>
       </c>
       <c r="M34" s="8">
-        <v>78.14</v>
-      </c>
-      <c r="N34" s="9">
-        <v>-1.57</v>
+        <v>85.51</v>
+      </c>
+      <c r="N34" s="10">
+        <v>9.43</v>
       </c>
       <c r="O34" s="10">
-        <v>37</v>
+        <v>33.4</v>
       </c>
       <c r="P34" s="8">
-        <v>157.5</v>
+        <v>243</v>
       </c>
       <c r="Q34" s="10">
-        <v>30.8</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2995,39 +3003,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="8">
-        <v>79.39</v>
+        <v>78.14</v>
       </c>
       <c r="I35" s="9">
-        <v>-7.65</v>
+        <v>-1.57</v>
       </c>
       <c r="J35" s="10">
-        <v>25.1</v>
+        <v>37</v>
       </c>
       <c r="K35" s="8">
-        <v>79.39</v>
+        <v>157.5</v>
       </c>
       <c r="L35" s="10">
-        <v>25.1</v>
+        <v>30.8</v>
       </c>
       <c r="M35" s="8">
-        <v>79.39</v>
+        <v>78.14</v>
       </c>
       <c r="N35" s="9">
-        <v>-7.65</v>
+        <v>-1.57</v>
       </c>
       <c r="O35" s="10">
-        <v>25.1</v>
+        <v>37</v>
       </c>
       <c r="P35" s="8">
-        <v>79.39</v>
+        <v>157.5</v>
       </c>
       <c r="Q35" s="10">
-        <v>25.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3048,39 +3056,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="8">
-        <v>85.96</v>
-      </c>
-      <c r="I36" s="10">
-        <v>1.39</v>
+        <v>79.39</v>
+      </c>
+      <c r="I36" s="9">
+        <v>-7.65</v>
       </c>
       <c r="J36" s="10">
-        <v>26.6</v>
+        <v>25.1</v>
       </c>
       <c r="K36" s="8">
-        <v>889.9</v>
+        <v>79.39</v>
       </c>
       <c r="L36" s="10">
-        <v>1.79</v>
+        <v>25.1</v>
       </c>
       <c r="M36" s="8">
-        <v>85.96</v>
-      </c>
-      <c r="N36" s="10">
-        <v>1.39</v>
+        <v>79.39</v>
+      </c>
+      <c r="N36" s="9">
+        <v>-7.65</v>
       </c>
       <c r="O36" s="10">
-        <v>26.6</v>
+        <v>25.1</v>
       </c>
       <c r="P36" s="8">
-        <v>889.9</v>
+        <v>79.39</v>
       </c>
       <c r="Q36" s="10">
-        <v>1.79</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3101,39 +3109,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="8">
-        <v>84.78</v>
+        <v>85.96</v>
       </c>
       <c r="I37" s="10">
-        <v>2.94</v>
+        <v>1.39</v>
       </c>
       <c r="J37" s="10">
-        <v>9.27</v>
+        <v>26.6</v>
       </c>
       <c r="K37" s="8">
-        <v>803.9</v>
-      </c>
-      <c r="L37" s="9">
-        <v>-0.28999999999999998</v>
+        <v>889.9</v>
+      </c>
+      <c r="L37" s="10">
+        <v>1.79</v>
       </c>
       <c r="M37" s="8">
-        <v>84.78</v>
+        <v>85.96</v>
       </c>
       <c r="N37" s="10">
-        <v>2.94</v>
+        <v>1.39</v>
       </c>
       <c r="O37" s="10">
-        <v>9.27</v>
+        <v>26.6</v>
       </c>
       <c r="P37" s="8">
-        <v>803.9</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>-0.28999999999999998</v>
+        <v>889.9</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>1.79</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3154,39 +3162,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="8">
-        <v>82.35</v>
-      </c>
-      <c r="I38" s="9">
-        <v>-0.41</v>
+        <v>84.78</v>
+      </c>
+      <c r="I38" s="10">
+        <v>2.94</v>
       </c>
       <c r="J38" s="10">
-        <v>2.75</v>
+        <v>9.27</v>
       </c>
       <c r="K38" s="8">
-        <v>719.1</v>
+        <v>803.9</v>
       </c>
       <c r="L38" s="9">
-        <v>-1.31</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M38" s="8">
-        <v>82.35</v>
-      </c>
-      <c r="N38" s="9">
-        <v>-0.41</v>
+        <v>84.78</v>
+      </c>
+      <c r="N38" s="10">
+        <v>2.94</v>
       </c>
       <c r="O38" s="10">
-        <v>2.75</v>
+        <v>9.27</v>
       </c>
       <c r="P38" s="8">
-        <v>719.1</v>
+        <v>803.9</v>
       </c>
       <c r="Q38" s="9">
-        <v>-1.31</v>
+        <v>-0.28999999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3207,39 +3215,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="8">
-        <v>82.69</v>
-      </c>
-      <c r="I39" s="10">
-        <v>4.3499999999999996</v>
+        <v>82.35</v>
+      </c>
+      <c r="I39" s="9">
+        <v>-0.41</v>
       </c>
       <c r="J39" s="10">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="K39" s="8">
-        <v>636.79999999999995</v>
+        <v>719.1</v>
       </c>
       <c r="L39" s="9">
-        <v>-1.81</v>
+        <v>-1.31</v>
       </c>
       <c r="M39" s="8">
-        <v>82.69</v>
-      </c>
-      <c r="N39" s="10">
-        <v>4.3499999999999996</v>
+        <v>82.35</v>
+      </c>
+      <c r="N39" s="9">
+        <v>-0.41</v>
       </c>
       <c r="O39" s="10">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="P39" s="8">
-        <v>636.79999999999995</v>
+        <v>719.1</v>
       </c>
       <c r="Q39" s="9">
-        <v>-1.81</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3260,39 +3268,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="8">
-        <v>79.239999999999995</v>
+        <v>82.69</v>
       </c>
       <c r="I40" s="10">
-        <v>3.32</v>
-      </c>
-      <c r="J40" s="9">
-        <v>-0.49</v>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="J40" s="10">
+        <v>6.2</v>
       </c>
       <c r="K40" s="8">
-        <v>554.1</v>
+        <v>636.79999999999995</v>
       </c>
       <c r="L40" s="9">
-        <v>-2.9</v>
+        <v>-1.81</v>
       </c>
       <c r="M40" s="8">
-        <v>79.239999999999995</v>
+        <v>82.69</v>
       </c>
       <c r="N40" s="10">
-        <v>3.32</v>
-      </c>
-      <c r="O40" s="9">
-        <v>-0.49</v>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="O40" s="10">
+        <v>6.2</v>
       </c>
       <c r="P40" s="8">
-        <v>554.1</v>
+        <v>636.79999999999995</v>
       </c>
       <c r="Q40" s="9">
-        <v>-2.9</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3313,39 +3321,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="8">
-        <v>76.69</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="I41" s="10">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="J41" s="9">
-        <v>-3.4</v>
+        <v>-0.49</v>
       </c>
       <c r="K41" s="8">
-        <v>474.9</v>
+        <v>554.1</v>
       </c>
       <c r="L41" s="9">
-        <v>-3.29</v>
+        <v>-2.9</v>
       </c>
       <c r="M41" s="8">
-        <v>76.69</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="N41" s="10">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="O41" s="9">
-        <v>-3.4</v>
+        <v>-0.49</v>
       </c>
       <c r="P41" s="8">
-        <v>474.9</v>
+        <v>554.1</v>
       </c>
       <c r="Q41" s="9">
-        <v>-3.29</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3366,39 +3374,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="8">
-        <v>74.459999999999994</v>
+        <v>76.69</v>
       </c>
       <c r="I42" s="10">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="J42" s="9">
-        <v>-1.56</v>
+        <v>-3.4</v>
       </c>
       <c r="K42" s="8">
-        <v>398.2</v>
+        <v>474.9</v>
       </c>
       <c r="L42" s="9">
-        <v>-3.27</v>
+        <v>-3.29</v>
       </c>
       <c r="M42" s="8">
-        <v>74.459999999999994</v>
+        <v>76.69</v>
       </c>
       <c r="N42" s="10">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="O42" s="9">
-        <v>-1.56</v>
+        <v>-3.4</v>
       </c>
       <c r="P42" s="8">
-        <v>398.2</v>
+        <v>474.9</v>
       </c>
       <c r="Q42" s="9">
-        <v>-3.27</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3419,39 +3427,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="8">
-        <v>72.31</v>
+        <v>74.459999999999994</v>
       </c>
       <c r="I43" s="10">
-        <v>8.18</v>
+        <v>2.97</v>
       </c>
       <c r="J43" s="9">
-        <v>-2.7</v>
+        <v>-1.56</v>
       </c>
       <c r="K43" s="8">
-        <v>323.7</v>
+        <v>398.2</v>
       </c>
       <c r="L43" s="9">
-        <v>-3.66</v>
+        <v>-3.27</v>
       </c>
       <c r="M43" s="8">
-        <v>72.31</v>
+        <v>74.459999999999994</v>
       </c>
       <c r="N43" s="10">
-        <v>8.18</v>
+        <v>2.97</v>
       </c>
       <c r="O43" s="9">
-        <v>-2.7</v>
+        <v>-1.56</v>
       </c>
       <c r="P43" s="8">
-        <v>323.7</v>
+        <v>398.2</v>
       </c>
       <c r="Q43" s="9">
-        <v>-3.66</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3472,39 +3480,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="8">
-        <v>66.84</v>
+        <v>72.31</v>
       </c>
       <c r="I44" s="10">
-        <v>4.28</v>
+        <v>8.18</v>
       </c>
       <c r="J44" s="9">
-        <v>-7.89</v>
+        <v>-2.7</v>
       </c>
       <c r="K44" s="8">
-        <v>251.4</v>
+        <v>323.7</v>
       </c>
       <c r="L44" s="9">
-        <v>-3.93</v>
+        <v>-3.66</v>
       </c>
       <c r="M44" s="8">
-        <v>66.84</v>
+        <v>72.31</v>
       </c>
       <c r="N44" s="10">
-        <v>4.28</v>
+        <v>8.18</v>
       </c>
       <c r="O44" s="9">
-        <v>-7.89</v>
+        <v>-2.7</v>
       </c>
       <c r="P44" s="8">
-        <v>251.4</v>
+        <v>323.7</v>
       </c>
       <c r="Q44" s="9">
-        <v>-3.93</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3525,39 +3533,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="8">
-        <v>64.09</v>
+        <v>66.84</v>
       </c>
       <c r="I45" s="10">
-        <v>12.4</v>
+        <v>4.28</v>
       </c>
       <c r="J45" s="9">
-        <v>-5.85</v>
+        <v>-7.89</v>
       </c>
       <c r="K45" s="8">
-        <v>184.6</v>
+        <v>251.4</v>
       </c>
       <c r="L45" s="9">
-        <v>-2.41</v>
+        <v>-3.93</v>
       </c>
       <c r="M45" s="8">
-        <v>64.09</v>
+        <v>66.84</v>
       </c>
       <c r="N45" s="10">
-        <v>12.4</v>
+        <v>4.28</v>
       </c>
       <c r="O45" s="9">
-        <v>-5.85</v>
+        <v>-7.89</v>
       </c>
       <c r="P45" s="8">
-        <v>184.6</v>
+        <v>251.4</v>
       </c>
       <c r="Q45" s="9">
-        <v>-2.41</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3578,39 +3586,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="8">
-        <v>57.02</v>
-      </c>
-      <c r="I46" s="9">
-        <v>-10.1</v>
+        <v>64.09</v>
+      </c>
+      <c r="I46" s="10">
+        <v>12.4</v>
       </c>
       <c r="J46" s="9">
-        <v>-2.98</v>
+        <v>-5.85</v>
       </c>
       <c r="K46" s="8">
-        <v>120.5</v>
+        <v>184.6</v>
       </c>
       <c r="L46" s="9">
-        <v>-0.48</v>
+        <v>-2.41</v>
       </c>
       <c r="M46" s="8">
-        <v>57.02</v>
-      </c>
-      <c r="N46" s="9">
-        <v>-10.1</v>
+        <v>64.09</v>
+      </c>
+      <c r="N46" s="10">
+        <v>12.4</v>
       </c>
       <c r="O46" s="9">
-        <v>-2.98</v>
+        <v>-5.85</v>
       </c>
       <c r="P46" s="8">
-        <v>120.5</v>
+        <v>184.6</v>
       </c>
       <c r="Q46" s="9">
-        <v>-0.48</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3631,39 +3639,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="8">
-        <v>63.44</v>
+        <v>57.02</v>
       </c>
       <c r="I47" s="9">
-        <v>-6.54</v>
-      </c>
-      <c r="J47" s="10">
-        <v>1.87</v>
+        <v>-10.1</v>
+      </c>
+      <c r="J47" s="9">
+        <v>-2.98</v>
       </c>
       <c r="K47" s="8">
-        <v>63.44</v>
-      </c>
-      <c r="L47" s="10">
-        <v>1.87</v>
+        <v>120.5</v>
+      </c>
+      <c r="L47" s="9">
+        <v>-0.48</v>
       </c>
       <c r="M47" s="8">
-        <v>63.44</v>
+        <v>57.02</v>
       </c>
       <c r="N47" s="9">
-        <v>-6.54</v>
-      </c>
-      <c r="O47" s="10">
-        <v>1.87</v>
+        <v>-10.1</v>
+      </c>
+      <c r="O47" s="9">
+        <v>-2.98</v>
       </c>
       <c r="P47" s="8">
-        <v>63.44</v>
-      </c>
-      <c r="Q47" s="10">
-        <v>1.87</v>
+        <v>120.5</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3684,39 +3692,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="8">
-        <v>67.89</v>
+        <v>63.44</v>
       </c>
       <c r="I48" s="9">
-        <v>-12.5</v>
-      </c>
-      <c r="J48" s="9">
-        <v>-4.0599999999999996</v>
+        <v>-6.54</v>
+      </c>
+      <c r="J48" s="10">
+        <v>1.87</v>
       </c>
       <c r="K48" s="8">
-        <v>874.2</v>
+        <v>63.44</v>
       </c>
       <c r="L48" s="10">
-        <v>4.62</v>
+        <v>1.87</v>
       </c>
       <c r="M48" s="8">
-        <v>67.89</v>
+        <v>63.44</v>
       </c>
       <c r="N48" s="9">
-        <v>-12.5</v>
-      </c>
-      <c r="O48" s="9">
-        <v>-4.0599999999999996</v>
+        <v>-6.54</v>
+      </c>
+      <c r="O48" s="10">
+        <v>1.87</v>
       </c>
       <c r="P48" s="8">
-        <v>874.2</v>
+        <v>63.44</v>
       </c>
       <c r="Q48" s="10">
-        <v>4.62</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3737,39 +3745,39 @@
         <v>17</v>
       </c>
       <c r="H49" s="8">
-        <v>77.59</v>
+        <v>67.89</v>
       </c>
       <c r="I49" s="9">
-        <v>-3.19</v>
-      </c>
-      <c r="J49" s="10">
-        <v>8.7100000000000009</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J49" s="9">
+        <v>-4.0599999999999996</v>
       </c>
       <c r="K49" s="8">
-        <v>806.3</v>
+        <v>874.2</v>
       </c>
       <c r="L49" s="10">
-        <v>5.42</v>
+        <v>4.62</v>
       </c>
       <c r="M49" s="8">
-        <v>77.59</v>
+        <v>67.89</v>
       </c>
       <c r="N49" s="9">
-        <v>-3.19</v>
-      </c>
-      <c r="O49" s="10">
-        <v>8.7100000000000009</v>
+        <v>-12.5</v>
+      </c>
+      <c r="O49" s="9">
+        <v>-4.0599999999999996</v>
       </c>
       <c r="P49" s="8">
-        <v>806.3</v>
+        <v>874.2</v>
       </c>
       <c r="Q49" s="10">
-        <v>5.42</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3790,39 +3798,39 @@
         <v>17</v>
       </c>
       <c r="H50" s="8">
-        <v>80.150000000000006</v>
-      </c>
-      <c r="I50" s="10">
-        <v>2.93</v>
+        <v>77.59</v>
+      </c>
+      <c r="I50" s="9">
+        <v>-3.19</v>
       </c>
       <c r="J50" s="10">
-        <v>8.17</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="K50" s="8">
-        <v>728.7</v>
+        <v>806.3</v>
       </c>
       <c r="L50" s="10">
-        <v>5.08</v>
+        <v>5.42</v>
       </c>
       <c r="M50" s="8">
-        <v>80.150000000000006</v>
-      </c>
-      <c r="N50" s="10">
-        <v>2.93</v>
+        <v>77.59</v>
+      </c>
+      <c r="N50" s="9">
+        <v>-3.19</v>
       </c>
       <c r="O50" s="10">
-        <v>8.17</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="P50" s="8">
-        <v>728.7</v>
+        <v>806.3</v>
       </c>
       <c r="Q50" s="10">
-        <v>5.08</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3843,39 +3851,39 @@
         <v>17</v>
       </c>
       <c r="H51" s="8">
-        <v>77.86</v>
-      </c>
-      <c r="I51" s="9">
-        <v>-2.2200000000000002</v>
+        <v>80.150000000000006</v>
+      </c>
+      <c r="I51" s="10">
+        <v>2.93</v>
       </c>
       <c r="J51" s="10">
-        <v>6.39</v>
+        <v>8.17</v>
       </c>
       <c r="K51" s="8">
-        <v>648.5</v>
+        <v>728.7</v>
       </c>
       <c r="L51" s="10">
-        <v>4.71</v>
+        <v>5.08</v>
       </c>
       <c r="M51" s="8">
-        <v>77.86</v>
-      </c>
-      <c r="N51" s="9">
-        <v>-2.2200000000000002</v>
+        <v>80.150000000000006</v>
+      </c>
+      <c r="N51" s="10">
+        <v>2.93</v>
       </c>
       <c r="O51" s="10">
-        <v>6.39</v>
+        <v>8.17</v>
       </c>
       <c r="P51" s="8">
-        <v>648.5</v>
+        <v>728.7</v>
       </c>
       <c r="Q51" s="10">
-        <v>4.71</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3896,39 +3904,39 @@
         <v>17</v>
       </c>
       <c r="H52" s="8">
-        <v>79.63</v>
-      </c>
-      <c r="I52" s="10">
-        <v>0.28999999999999998</v>
+        <v>77.86</v>
+      </c>
+      <c r="I52" s="9">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="J52" s="10">
-        <v>7.95</v>
+        <v>6.39</v>
       </c>
       <c r="K52" s="8">
-        <v>570.70000000000005</v>
+        <v>648.5</v>
       </c>
       <c r="L52" s="10">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
       <c r="M52" s="8">
-        <v>79.63</v>
-      </c>
-      <c r="N52" s="10">
-        <v>0.28999999999999998</v>
+        <v>77.86</v>
+      </c>
+      <c r="N52" s="9">
+        <v>-2.2200000000000002</v>
       </c>
       <c r="O52" s="10">
-        <v>7.95</v>
+        <v>6.39</v>
       </c>
       <c r="P52" s="8">
-        <v>570.70000000000005</v>
+        <v>648.5</v>
       </c>
       <c r="Q52" s="10">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3949,39 +3957,39 @@
         <v>17</v>
       </c>
       <c r="H53" s="8">
-        <v>79.400000000000006</v>
+        <v>79.63</v>
       </c>
       <c r="I53" s="10">
-        <v>4.96</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J53" s="10">
-        <v>9.35</v>
+        <v>7.95</v>
       </c>
       <c r="K53" s="8">
-        <v>491.1</v>
+        <v>570.70000000000005</v>
       </c>
       <c r="L53" s="10">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
       <c r="M53" s="8">
-        <v>79.400000000000006</v>
+        <v>79.63</v>
       </c>
       <c r="N53" s="10">
-        <v>4.96</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O53" s="10">
-        <v>9.35</v>
+        <v>7.95</v>
       </c>
       <c r="P53" s="8">
-        <v>491.1</v>
+        <v>570.70000000000005</v>
       </c>
       <c r="Q53" s="10">
-        <v>3.95</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4002,39 +4010,39 @@
         <v>17</v>
       </c>
       <c r="H54" s="8">
-        <v>75.64</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="I54" s="10">
-        <v>1.77</v>
+        <v>4.96</v>
       </c>
       <c r="J54" s="10">
-        <v>9.98</v>
+        <v>9.35</v>
       </c>
       <c r="K54" s="8">
-        <v>411.7</v>
+        <v>491.1</v>
       </c>
       <c r="L54" s="10">
-        <v>2.97</v>
+        <v>3.95</v>
       </c>
       <c r="M54" s="8">
-        <v>75.64</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="N54" s="10">
-        <v>1.77</v>
+        <v>4.96</v>
       </c>
       <c r="O54" s="10">
-        <v>9.98</v>
+        <v>9.35</v>
       </c>
       <c r="P54" s="8">
-        <v>411.7</v>
+        <v>491.1</v>
       </c>
       <c r="Q54" s="10">
-        <v>2.97</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4055,39 +4063,39 @@
         <v>17</v>
       </c>
       <c r="H55" s="8">
-        <v>74.319999999999993</v>
+        <v>75.64</v>
       </c>
       <c r="I55" s="10">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="J55" s="10">
-        <v>6.27</v>
+        <v>9.98</v>
       </c>
       <c r="K55" s="8">
-        <v>336</v>
+        <v>411.7</v>
       </c>
       <c r="L55" s="10">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
       <c r="M55" s="8">
-        <v>74.319999999999993</v>
+        <v>75.64</v>
       </c>
       <c r="N55" s="10">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O55" s="10">
-        <v>6.27</v>
+        <v>9.98</v>
       </c>
       <c r="P55" s="8">
-        <v>336</v>
+        <v>411.7</v>
       </c>
       <c r="Q55" s="10">
-        <v>1.51</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4108,39 +4116,39 @@
         <v>17</v>
       </c>
       <c r="H56" s="8">
-        <v>72.56</v>
+        <v>74.319999999999993</v>
       </c>
       <c r="I56" s="10">
-        <v>6.58</v>
+        <v>2.42</v>
       </c>
       <c r="J56" s="10">
-        <v>10.7</v>
+        <v>6.27</v>
       </c>
       <c r="K56" s="8">
-        <v>261.7</v>
+        <v>336</v>
       </c>
       <c r="L56" s="10">
-        <v>0.24</v>
+        <v>1.51</v>
       </c>
       <c r="M56" s="8">
-        <v>72.56</v>
+        <v>74.319999999999993</v>
       </c>
       <c r="N56" s="10">
-        <v>6.58</v>
+        <v>2.42</v>
       </c>
       <c r="O56" s="10">
-        <v>10.7</v>
+        <v>6.27</v>
       </c>
       <c r="P56" s="8">
-        <v>261.7</v>
+        <v>336</v>
       </c>
       <c r="Q56" s="10">
-        <v>0.24</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4161,39 +4169,39 @@
         <v>17</v>
       </c>
       <c r="H57" s="8">
-        <v>68.08</v>
+        <v>72.56</v>
       </c>
       <c r="I57" s="10">
-        <v>15.8</v>
+        <v>6.58</v>
       </c>
       <c r="J57" s="10">
-        <v>2.09</v>
+        <v>10.7</v>
       </c>
       <c r="K57" s="8">
-        <v>189.1</v>
-      </c>
-      <c r="L57" s="9">
-        <v>-3.26</v>
+        <v>261.7</v>
+      </c>
+      <c r="L57" s="10">
+        <v>0.24</v>
       </c>
       <c r="M57" s="8">
-        <v>68.08</v>
+        <v>72.56</v>
       </c>
       <c r="N57" s="10">
-        <v>15.8</v>
+        <v>6.58</v>
       </c>
       <c r="O57" s="10">
-        <v>2.09</v>
+        <v>10.7</v>
       </c>
       <c r="P57" s="8">
-        <v>189.1</v>
-      </c>
-      <c r="Q57" s="9">
-        <v>-3.26</v>
+        <v>261.7</v>
+      </c>
+      <c r="Q57" s="10">
+        <v>0.24</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4214,39 +4222,39 @@
         <v>17</v>
       </c>
       <c r="H58" s="8">
-        <v>58.77</v>
-      </c>
-      <c r="I58" s="9">
-        <v>-5.62</v>
-      </c>
-      <c r="J58" s="9">
-        <v>-2.08</v>
+        <v>68.08</v>
+      </c>
+      <c r="I58" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="J58" s="10">
+        <v>2.09</v>
       </c>
       <c r="K58" s="8">
-        <v>121.1</v>
+        <v>189.1</v>
       </c>
       <c r="L58" s="9">
-        <v>-6.04</v>
+        <v>-3.26</v>
       </c>
       <c r="M58" s="8">
-        <v>58.77</v>
-      </c>
-      <c r="N58" s="9">
-        <v>-5.62</v>
-      </c>
-      <c r="O58" s="9">
-        <v>-2.08</v>
+        <v>68.08</v>
+      </c>
+      <c r="N58" s="10">
+        <v>15.8</v>
+      </c>
+      <c r="O58" s="10">
+        <v>2.09</v>
       </c>
       <c r="P58" s="8">
-        <v>121.1</v>
+        <v>189.1</v>
       </c>
       <c r="Q58" s="9">
-        <v>-6.04</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4267,39 +4275,39 @@
         <v>17</v>
       </c>
       <c r="H59" s="8">
-        <v>62.28</v>
+        <v>58.77</v>
       </c>
       <c r="I59" s="9">
-        <v>-12</v>
+        <v>-5.62</v>
       </c>
       <c r="J59" s="9">
-        <v>-9.49</v>
+        <v>-2.08</v>
       </c>
       <c r="K59" s="8">
-        <v>62.28</v>
+        <v>121.1</v>
       </c>
       <c r="L59" s="9">
-        <v>-9.49</v>
+        <v>-6.04</v>
       </c>
       <c r="M59" s="8">
-        <v>62.28</v>
+        <v>58.77</v>
       </c>
       <c r="N59" s="9">
-        <v>-12</v>
+        <v>-5.62</v>
       </c>
       <c r="O59" s="9">
-        <v>-9.49</v>
+        <v>-2.08</v>
       </c>
       <c r="P59" s="8">
-        <v>62.28</v>
+        <v>121.1</v>
       </c>
       <c r="Q59" s="9">
-        <v>-9.49</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4320,39 +4328,39 @@
         <v>17</v>
       </c>
       <c r="H60" s="8">
-        <v>70.77</v>
+        <v>62.28</v>
       </c>
       <c r="I60" s="9">
-        <v>-0.84</v>
+        <v>-12</v>
       </c>
       <c r="J60" s="9">
-        <v>-5.24</v>
+        <v>-9.49</v>
       </c>
       <c r="K60" s="8">
-        <v>835.5</v>
+        <v>62.28</v>
       </c>
       <c r="L60" s="9">
-        <v>-1.82</v>
+        <v>-9.49</v>
       </c>
       <c r="M60" s="8">
-        <v>70.77</v>
+        <v>62.28</v>
       </c>
       <c r="N60" s="9">
-        <v>-0.84</v>
+        <v>-12</v>
       </c>
       <c r="O60" s="9">
-        <v>-5.24</v>
+        <v>-9.49</v>
       </c>
       <c r="P60" s="8">
-        <v>835.5</v>
+        <v>62.28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-1.82</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4373,39 +4381,39 @@
         <v>17</v>
       </c>
       <c r="H61" s="8">
-        <v>71.37</v>
+        <v>70.77</v>
       </c>
       <c r="I61" s="9">
-        <v>-3.67</v>
+        <v>-0.84</v>
       </c>
       <c r="J61" s="9">
-        <v>-1.84</v>
+        <v>-5.24</v>
       </c>
       <c r="K61" s="8">
-        <v>764.8</v>
+        <v>835.5</v>
       </c>
       <c r="L61" s="9">
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
       <c r="M61" s="8">
-        <v>71.37</v>
+        <v>70.77</v>
       </c>
       <c r="N61" s="9">
-        <v>-3.67</v>
+        <v>-0.84</v>
       </c>
       <c r="O61" s="9">
-        <v>-1.84</v>
+        <v>-5.24</v>
       </c>
       <c r="P61" s="8">
-        <v>764.8</v>
+        <v>835.5</v>
       </c>
       <c r="Q61" s="9">
-        <v>-1.5</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4426,39 +4434,39 @@
         <v>17</v>
       </c>
       <c r="H62" s="8">
-        <v>74.09</v>
-      </c>
-      <c r="I62" s="10">
-        <v>1.24</v>
+        <v>71.37</v>
+      </c>
+      <c r="I62" s="9">
+        <v>-3.67</v>
       </c>
       <c r="J62" s="9">
-        <v>-0.38</v>
+        <v>-1.84</v>
       </c>
       <c r="K62" s="8">
-        <v>693.4</v>
+        <v>764.8</v>
       </c>
       <c r="L62" s="9">
-        <v>-1.46</v>
+        <v>-1.5</v>
       </c>
       <c r="M62" s="8">
-        <v>74.09</v>
-      </c>
-      <c r="N62" s="10">
-        <v>1.24</v>
+        <v>71.37</v>
+      </c>
+      <c r="N62" s="9">
+        <v>-3.67</v>
       </c>
       <c r="O62" s="9">
-        <v>-0.38</v>
+        <v>-1.84</v>
       </c>
       <c r="P62" s="8">
-        <v>693.4</v>
+        <v>764.8</v>
       </c>
       <c r="Q62" s="9">
-        <v>-1.46</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4479,39 +4487,39 @@
         <v>17</v>
       </c>
       <c r="H63" s="8">
-        <v>73.180000000000007</v>
-      </c>
-      <c r="I63" s="9">
-        <v>-0.78</v>
-      </c>
-      <c r="J63" s="10">
-        <v>1.54</v>
+        <v>74.09</v>
+      </c>
+      <c r="I63" s="10">
+        <v>1.24</v>
+      </c>
+      <c r="J63" s="9">
+        <v>-0.38</v>
       </c>
       <c r="K63" s="8">
-        <v>619.29999999999995</v>
+        <v>693.4</v>
       </c>
       <c r="L63" s="9">
-        <v>-1.59</v>
+        <v>-1.46</v>
       </c>
       <c r="M63" s="8">
-        <v>73.180000000000007</v>
-      </c>
-      <c r="N63" s="9">
-        <v>-0.78</v>
-      </c>
-      <c r="O63" s="10">
-        <v>1.54</v>
+        <v>74.09</v>
+      </c>
+      <c r="N63" s="10">
+        <v>1.24</v>
+      </c>
+      <c r="O63" s="9">
+        <v>-0.38</v>
       </c>
       <c r="P63" s="8">
-        <v>619.29999999999995</v>
+        <v>693.4</v>
       </c>
       <c r="Q63" s="9">
-        <v>-1.59</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4532,39 +4540,39 @@
         <v>17</v>
       </c>
       <c r="H64" s="8">
-        <v>73.760000000000005</v>
-      </c>
-      <c r="I64" s="10">
-        <v>1.59</v>
-      </c>
-      <c r="J64" s="9">
-        <v>-0.75</v>
+        <v>73.180000000000007</v>
+      </c>
+      <c r="I64" s="9">
+        <v>-0.78</v>
+      </c>
+      <c r="J64" s="10">
+        <v>1.54</v>
       </c>
       <c r="K64" s="8">
-        <v>546.1</v>
+        <v>619.29999999999995</v>
       </c>
       <c r="L64" s="9">
-        <v>-1.99</v>
+        <v>-1.59</v>
       </c>
       <c r="M64" s="8">
-        <v>73.760000000000005</v>
-      </c>
-      <c r="N64" s="10">
-        <v>1.59</v>
-      </c>
-      <c r="O64" s="9">
-        <v>-0.75</v>
+        <v>73.180000000000007</v>
+      </c>
+      <c r="N64" s="9">
+        <v>-0.78</v>
+      </c>
+      <c r="O64" s="10">
+        <v>1.54</v>
       </c>
       <c r="P64" s="8">
-        <v>546.1</v>
+        <v>619.29999999999995</v>
       </c>
       <c r="Q64" s="9">
-        <v>-1.99</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4585,39 +4593,39 @@
         <v>17</v>
       </c>
       <c r="H65" s="8">
-        <v>72.61</v>
+        <v>73.760000000000005</v>
       </c>
       <c r="I65" s="10">
-        <v>5.56</v>
+        <v>1.59</v>
       </c>
       <c r="J65" s="9">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="K65" s="8">
-        <v>472.4</v>
+        <v>546.1</v>
       </c>
       <c r="L65" s="9">
-        <v>-2.1800000000000002</v>
+        <v>-1.99</v>
       </c>
       <c r="M65" s="8">
-        <v>72.61</v>
+        <v>73.760000000000005</v>
       </c>
       <c r="N65" s="10">
-        <v>5.56</v>
+        <v>1.59</v>
       </c>
       <c r="O65" s="9">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="P65" s="8">
-        <v>472.4</v>
+        <v>546.1</v>
       </c>
       <c r="Q65" s="9">
-        <v>-2.1800000000000002</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4638,39 +4646,39 @@
         <v>17</v>
       </c>
       <c r="H66" s="8">
-        <v>68.78</v>
-      </c>
-      <c r="I66" s="9">
-        <v>-1.64</v>
+        <v>72.61</v>
+      </c>
+      <c r="I66" s="10">
+        <v>5.56</v>
       </c>
       <c r="J66" s="9">
-        <v>-6.96</v>
+        <v>-0.74</v>
       </c>
       <c r="K66" s="8">
-        <v>399.8</v>
+        <v>472.4</v>
       </c>
       <c r="L66" s="9">
-        <v>-2.44</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="M66" s="8">
-        <v>68.78</v>
-      </c>
-      <c r="N66" s="9">
-        <v>-1.64</v>
+        <v>72.61</v>
+      </c>
+      <c r="N66" s="10">
+        <v>5.56</v>
       </c>
       <c r="O66" s="9">
-        <v>-6.96</v>
+        <v>-0.74</v>
       </c>
       <c r="P66" s="8">
-        <v>399.8</v>
+        <v>472.4</v>
       </c>
       <c r="Q66" s="9">
-        <v>-2.44</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4691,39 +4699,39 @@
         <v>17</v>
       </c>
       <c r="H67" s="8">
-        <v>69.930000000000007</v>
-      </c>
-      <c r="I67" s="10">
-        <v>6.7</v>
+        <v>68.78</v>
+      </c>
+      <c r="I67" s="9">
+        <v>-1.64</v>
       </c>
       <c r="J67" s="9">
-        <v>-6.27</v>
+        <v>-6.96</v>
       </c>
       <c r="K67" s="8">
-        <v>331</v>
+        <v>399.8</v>
       </c>
       <c r="L67" s="9">
-        <v>-1.45</v>
+        <v>-2.44</v>
       </c>
       <c r="M67" s="8">
-        <v>69.930000000000007</v>
-      </c>
-      <c r="N67" s="10">
-        <v>6.7</v>
+        <v>68.78</v>
+      </c>
+      <c r="N67" s="9">
+        <v>-1.64</v>
       </c>
       <c r="O67" s="9">
-        <v>-6.27</v>
+        <v>-6.96</v>
       </c>
       <c r="P67" s="8">
-        <v>331</v>
+        <v>399.8</v>
       </c>
       <c r="Q67" s="9">
-        <v>-1.45</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4744,39 +4752,39 @@
         <v>17</v>
       </c>
       <c r="H68" s="8">
-        <v>65.540000000000006</v>
-      </c>
-      <c r="I68" s="9">
-        <v>-1.71</v>
+        <v>69.930000000000007</v>
+      </c>
+      <c r="I68" s="10">
+        <v>6.7</v>
       </c>
       <c r="J68" s="9">
-        <v>-3.99</v>
+        <v>-6.27</v>
       </c>
       <c r="K68" s="8">
-        <v>261.10000000000002</v>
+        <v>331</v>
       </c>
       <c r="L68" s="9">
-        <v>-7.0000000000000007E-2</v>
+        <v>-1.45</v>
       </c>
       <c r="M68" s="8">
-        <v>65.540000000000006</v>
-      </c>
-      <c r="N68" s="9">
-        <v>-1.71</v>
+        <v>69.930000000000007</v>
+      </c>
+      <c r="N68" s="10">
+        <v>6.7</v>
       </c>
       <c r="O68" s="9">
-        <v>-3.99</v>
+        <v>-6.27</v>
       </c>
       <c r="P68" s="8">
-        <v>261.10000000000002</v>
+        <v>331</v>
       </c>
       <c r="Q68" s="9">
-        <v>-7.0000000000000007E-2</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4797,39 +4805,39 @@
         <v>17</v>
       </c>
       <c r="H69" s="8">
-        <v>66.680000000000007</v>
-      </c>
-      <c r="I69" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="J69" s="10">
-        <v>3.84</v>
+        <v>65.540000000000006</v>
+      </c>
+      <c r="I69" s="9">
+        <v>-1.71</v>
+      </c>
+      <c r="J69" s="9">
+        <v>-3.99</v>
       </c>
       <c r="K69" s="8">
-        <v>195.5</v>
-      </c>
-      <c r="L69" s="10">
-        <v>1.3</v>
+        <v>261.10000000000002</v>
+      </c>
+      <c r="L69" s="9">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="M69" s="8">
-        <v>66.680000000000007</v>
-      </c>
-      <c r="N69" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="O69" s="10">
-        <v>3.84</v>
+        <v>65.540000000000006</v>
+      </c>
+      <c r="N69" s="9">
+        <v>-1.71</v>
+      </c>
+      <c r="O69" s="9">
+        <v>-3.99</v>
       </c>
       <c r="P69" s="8">
-        <v>195.5</v>
-      </c>
-      <c r="Q69" s="10">
-        <v>1.3</v>
+        <v>261.10000000000002</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>-7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4850,39 +4858,39 @@
         <v>17</v>
       </c>
       <c r="H70" s="8">
-        <v>60.02</v>
-      </c>
-      <c r="I70" s="9">
-        <v>-12.8</v>
-      </c>
-      <c r="J70" s="9">
-        <v>-3.89</v>
+        <v>66.680000000000007</v>
+      </c>
+      <c r="I70" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="J70" s="10">
+        <v>3.84</v>
       </c>
       <c r="K70" s="8">
-        <v>128.80000000000001</v>
+        <v>195.5</v>
       </c>
       <c r="L70" s="10">
-        <v>0.04</v>
+        <v>1.3</v>
       </c>
       <c r="M70" s="8">
-        <v>60.02</v>
-      </c>
-      <c r="N70" s="9">
-        <v>-12.8</v>
-      </c>
-      <c r="O70" s="9">
-        <v>-3.89</v>
+        <v>66.680000000000007</v>
+      </c>
+      <c r="N70" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="O70" s="10">
+        <v>3.84</v>
       </c>
       <c r="P70" s="8">
-        <v>128.80000000000001</v>
+        <v>195.5</v>
       </c>
       <c r="Q70" s="10">
-        <v>0.04</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4903,39 +4911,39 @@
         <v>17</v>
       </c>
       <c r="H71" s="8">
-        <v>68.81</v>
+        <v>60.02</v>
       </c>
       <c r="I71" s="9">
-        <v>-7.86</v>
-      </c>
-      <c r="J71" s="10">
-        <v>3.74</v>
+        <v>-12.8</v>
+      </c>
+      <c r="J71" s="9">
+        <v>-3.89</v>
       </c>
       <c r="K71" s="8">
-        <v>68.81</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="L71" s="10">
-        <v>3.74</v>
+        <v>0.04</v>
       </c>
       <c r="M71" s="8">
-        <v>68.81</v>
+        <v>60.02</v>
       </c>
       <c r="N71" s="9">
-        <v>-7.86</v>
-      </c>
-      <c r="O71" s="10">
-        <v>3.74</v>
+        <v>-12.8</v>
+      </c>
+      <c r="O71" s="9">
+        <v>-3.89</v>
       </c>
       <c r="P71" s="8">
-        <v>68.81</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="Q71" s="10">
-        <v>3.74</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4956,39 +4964,39 @@
         <v>17</v>
       </c>
       <c r="H72" s="8">
-        <v>74.69</v>
-      </c>
-      <c r="I72" s="10">
-        <v>2.71</v>
+        <v>68.81</v>
+      </c>
+      <c r="I72" s="9">
+        <v>-7.86</v>
       </c>
       <c r="J72" s="10">
-        <v>7.73</v>
+        <v>3.74</v>
       </c>
       <c r="K72" s="8">
-        <v>851.1</v>
+        <v>68.81</v>
       </c>
       <c r="L72" s="10">
-        <v>2.74</v>
+        <v>3.74</v>
       </c>
       <c r="M72" s="8">
-        <v>74.69</v>
-      </c>
-      <c r="N72" s="10">
-        <v>2.71</v>
+        <v>68.81</v>
+      </c>
+      <c r="N72" s="9">
+        <v>-7.86</v>
       </c>
       <c r="O72" s="10">
-        <v>7.73</v>
+        <v>3.74</v>
       </c>
       <c r="P72" s="8">
-        <v>851.1</v>
+        <v>68.81</v>
       </c>
       <c r="Q72" s="10">
-        <v>2.74</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5009,39 +5017,39 @@
         <v>17</v>
       </c>
       <c r="H73" s="8">
-        <v>72.709999999999994</v>
-      </c>
-      <c r="I73" s="9">
-        <v>-2.2400000000000002</v>
+        <v>74.69</v>
+      </c>
+      <c r="I73" s="10">
+        <v>2.71</v>
       </c>
       <c r="J73" s="10">
-        <v>7.43</v>
+        <v>7.73</v>
       </c>
       <c r="K73" s="8">
-        <v>776.4</v>
+        <v>851.1</v>
       </c>
       <c r="L73" s="10">
-        <v>2.2799999999999998</v>
+        <v>2.74</v>
       </c>
       <c r="M73" s="8">
-        <v>72.709999999999994</v>
-      </c>
-      <c r="N73" s="9">
-        <v>-2.2400000000000002</v>
+        <v>74.69</v>
+      </c>
+      <c r="N73" s="10">
+        <v>2.71</v>
       </c>
       <c r="O73" s="10">
-        <v>7.43</v>
+        <v>7.73</v>
       </c>
       <c r="P73" s="8">
-        <v>776.4</v>
+        <v>851.1</v>
       </c>
       <c r="Q73" s="10">
-        <v>2.2799999999999998</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5062,39 +5070,39 @@
         <v>17</v>
       </c>
       <c r="H74" s="8">
-        <v>74.38</v>
-      </c>
-      <c r="I74" s="10">
-        <v>3.2</v>
+        <v>72.709999999999994</v>
+      </c>
+      <c r="I74" s="9">
+        <v>-2.2400000000000002</v>
       </c>
       <c r="J74" s="10">
-        <v>5.27</v>
+        <v>7.43</v>
       </c>
       <c r="K74" s="8">
-        <v>703.7</v>
+        <v>776.4</v>
       </c>
       <c r="L74" s="10">
-        <v>1.78</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="M74" s="8">
-        <v>74.38</v>
-      </c>
-      <c r="N74" s="10">
-        <v>3.2</v>
+        <v>72.709999999999994</v>
+      </c>
+      <c r="N74" s="9">
+        <v>-2.2400000000000002</v>
       </c>
       <c r="O74" s="10">
-        <v>5.27</v>
+        <v>7.43</v>
       </c>
       <c r="P74" s="8">
-        <v>703.7</v>
+        <v>776.4</v>
       </c>
       <c r="Q74" s="10">
-        <v>1.78</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5115,39 +5123,39 @@
         <v>17</v>
       </c>
       <c r="H75" s="8">
-        <v>72.069999999999993</v>
-      </c>
-      <c r="I75" s="9">
-        <v>-3.03</v>
+        <v>74.38</v>
+      </c>
+      <c r="I75" s="10">
+        <v>3.2</v>
       </c>
       <c r="J75" s="10">
-        <v>3.48</v>
+        <v>5.27</v>
       </c>
       <c r="K75" s="8">
-        <v>629.29999999999995</v>
+        <v>703.7</v>
       </c>
       <c r="L75" s="10">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="M75" s="8">
-        <v>72.069999999999993</v>
-      </c>
-      <c r="N75" s="9">
-        <v>-3.03</v>
+        <v>74.38</v>
+      </c>
+      <c r="N75" s="10">
+        <v>3.2</v>
       </c>
       <c r="O75" s="10">
-        <v>3.48</v>
+        <v>5.27</v>
       </c>
       <c r="P75" s="8">
-        <v>629.29999999999995</v>
+        <v>703.7</v>
       </c>
       <c r="Q75" s="10">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5168,39 +5176,39 @@
         <v>17</v>
       </c>
       <c r="H76" s="8">
-        <v>74.33</v>
-      </c>
-      <c r="I76" s="10">
-        <v>1.6</v>
+        <v>72.069999999999993</v>
+      </c>
+      <c r="I76" s="9">
+        <v>-3.03</v>
       </c>
       <c r="J76" s="10">
-        <v>10.7</v>
+        <v>3.48</v>
       </c>
       <c r="K76" s="8">
-        <v>557.29999999999995</v>
+        <v>629.29999999999995</v>
       </c>
       <c r="L76" s="10">
-        <v>1.1100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="M76" s="8">
-        <v>74.33</v>
-      </c>
-      <c r="N76" s="10">
-        <v>1.6</v>
+        <v>72.069999999999993</v>
+      </c>
+      <c r="N76" s="9">
+        <v>-3.03</v>
       </c>
       <c r="O76" s="10">
-        <v>10.7</v>
+        <v>3.48</v>
       </c>
       <c r="P76" s="8">
-        <v>557.29999999999995</v>
+        <v>629.29999999999995</v>
       </c>
       <c r="Q76" s="10">
-        <v>1.1100000000000001</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5221,39 +5229,39 @@
         <v>17</v>
       </c>
       <c r="H77" s="8">
-        <v>73.150000000000006</v>
-      </c>
-      <c r="I77" s="9">
-        <v>-1.04</v>
+        <v>74.33</v>
+      </c>
+      <c r="I77" s="10">
+        <v>1.6</v>
       </c>
       <c r="J77" s="10">
-        <v>15.2</v>
+        <v>10.7</v>
       </c>
       <c r="K77" s="8">
-        <v>482.9</v>
-      </c>
-      <c r="L77" s="9">
-        <v>-0.21</v>
+        <v>557.29999999999995</v>
+      </c>
+      <c r="L77" s="10">
+        <v>1.1100000000000001</v>
       </c>
       <c r="M77" s="8">
-        <v>73.150000000000006</v>
-      </c>
-      <c r="N77" s="9">
-        <v>-1.04</v>
+        <v>74.33</v>
+      </c>
+      <c r="N77" s="10">
+        <v>1.6</v>
       </c>
       <c r="O77" s="10">
-        <v>15.2</v>
+        <v>10.7</v>
       </c>
       <c r="P77" s="8">
-        <v>482.9</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>-0.21</v>
+        <v>557.29999999999995</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5274,39 +5282,39 @@
         <v>17</v>
       </c>
       <c r="H78" s="8">
-        <v>73.930000000000007</v>
+        <v>73.150000000000006</v>
       </c>
       <c r="I78" s="9">
-        <v>-0.91</v>
+        <v>-1.04</v>
       </c>
       <c r="J78" s="10">
-        <v>7.49</v>
+        <v>15.2</v>
       </c>
       <c r="K78" s="8">
-        <v>409.8</v>
+        <v>482.9</v>
       </c>
       <c r="L78" s="9">
-        <v>-2.5299999999999998</v>
+        <v>-0.21</v>
       </c>
       <c r="M78" s="8">
-        <v>73.930000000000007</v>
+        <v>73.150000000000006</v>
       </c>
       <c r="N78" s="9">
-        <v>-0.91</v>
+        <v>-1.04</v>
       </c>
       <c r="O78" s="10">
-        <v>7.49</v>
+        <v>15.2</v>
       </c>
       <c r="P78" s="8">
-        <v>409.8</v>
+        <v>482.9</v>
       </c>
       <c r="Q78" s="9">
-        <v>-2.5299999999999998</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5327,39 +5335,39 @@
         <v>17</v>
       </c>
       <c r="H79" s="8">
-        <v>74.61</v>
-      </c>
-      <c r="I79" s="10">
-        <v>9.2899999999999991</v>
+        <v>73.930000000000007</v>
+      </c>
+      <c r="I79" s="9">
+        <v>-0.91</v>
       </c>
       <c r="J79" s="10">
-        <v>0.71</v>
+        <v>7.49</v>
       </c>
       <c r="K79" s="8">
-        <v>335.9</v>
+        <v>409.8</v>
       </c>
       <c r="L79" s="9">
-        <v>-4.49</v>
+        <v>-2.5299999999999998</v>
       </c>
       <c r="M79" s="8">
-        <v>74.61</v>
-      </c>
-      <c r="N79" s="10">
-        <v>9.2899999999999991</v>
+        <v>73.930000000000007</v>
+      </c>
+      <c r="N79" s="9">
+        <v>-0.91</v>
       </c>
       <c r="O79" s="10">
-        <v>0.71</v>
+        <v>7.49</v>
       </c>
       <c r="P79" s="8">
-        <v>335.9</v>
+        <v>409.8</v>
       </c>
       <c r="Q79" s="9">
-        <v>-4.49</v>
+        <v>-2.5299999999999998</v>
       </c>
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5380,39 +5388,39 @@
         <v>17</v>
       </c>
       <c r="H80" s="8">
-        <v>68.260000000000005</v>
+        <v>74.61</v>
       </c>
       <c r="I80" s="10">
-        <v>6.31</v>
-      </c>
-      <c r="J80" s="9">
-        <v>-1.85</v>
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="J80" s="10">
+        <v>0.71</v>
       </c>
       <c r="K80" s="8">
-        <v>261.3</v>
+        <v>335.9</v>
       </c>
       <c r="L80" s="9">
-        <v>-5.88</v>
+        <v>-4.49</v>
       </c>
       <c r="M80" s="8">
-        <v>68.260000000000005</v>
+        <v>74.61</v>
       </c>
       <c r="N80" s="10">
-        <v>6.31</v>
-      </c>
-      <c r="O80" s="9">
-        <v>-1.85</v>
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="O80" s="10">
+        <v>0.71</v>
       </c>
       <c r="P80" s="8">
-        <v>261.3</v>
+        <v>335.9</v>
       </c>
       <c r="Q80" s="9">
-        <v>-5.88</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5433,39 +5441,39 @@
         <v>17</v>
       </c>
       <c r="H81" s="8">
-        <v>64.209999999999994</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="I81" s="10">
-        <v>2.81</v>
+        <v>6.31</v>
       </c>
       <c r="J81" s="9">
-        <v>-13.7</v>
+        <v>-1.85</v>
       </c>
       <c r="K81" s="8">
-        <v>193</v>
+        <v>261.3</v>
       </c>
       <c r="L81" s="9">
-        <v>-7.23</v>
+        <v>-5.88</v>
       </c>
       <c r="M81" s="8">
-        <v>64.209999999999994</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="N81" s="10">
-        <v>2.81</v>
+        <v>6.31</v>
       </c>
       <c r="O81" s="9">
-        <v>-13.7</v>
+        <v>-1.85</v>
       </c>
       <c r="P81" s="8">
-        <v>193</v>
+        <v>261.3</v>
       </c>
       <c r="Q81" s="9">
-        <v>-7.23</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5486,39 +5494,39 @@
         <v>17</v>
       </c>
       <c r="H82" s="8">
-        <v>62.45</v>
-      </c>
-      <c r="I82" s="9">
-        <v>-5.83</v>
+        <v>64.209999999999994</v>
+      </c>
+      <c r="I82" s="10">
+        <v>2.81</v>
       </c>
       <c r="J82" s="9">
-        <v>-3.56</v>
+        <v>-13.7</v>
       </c>
       <c r="K82" s="8">
-        <v>128.80000000000001</v>
+        <v>193</v>
       </c>
       <c r="L82" s="9">
-        <v>-3.62</v>
+        <v>-7.23</v>
       </c>
       <c r="M82" s="8">
-        <v>62.45</v>
-      </c>
-      <c r="N82" s="9">
-        <v>-5.83</v>
+        <v>64.209999999999994</v>
+      </c>
+      <c r="N82" s="10">
+        <v>2.81</v>
       </c>
       <c r="O82" s="9">
-        <v>-3.56</v>
+        <v>-13.7</v>
       </c>
       <c r="P82" s="8">
-        <v>128.80000000000001</v>
+        <v>193</v>
       </c>
       <c r="Q82" s="9">
-        <v>-3.62</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>17</v>
@@ -5539,39 +5547,39 @@
         <v>17</v>
       </c>
       <c r="H83" s="8">
-        <v>66.33</v>
+        <v>62.45</v>
       </c>
       <c r="I83" s="9">
-        <v>-4.32</v>
+        <v>-5.83</v>
       </c>
       <c r="J83" s="9">
-        <v>-3.67</v>
+        <v>-3.56</v>
       </c>
       <c r="K83" s="8">
-        <v>66.33</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="L83" s="9">
-        <v>-3.67</v>
+        <v>-3.62</v>
       </c>
       <c r="M83" s="8">
-        <v>66.33</v>
+        <v>62.45</v>
       </c>
       <c r="N83" s="9">
-        <v>-4.32</v>
+        <v>-5.83</v>
       </c>
       <c r="O83" s="9">
-        <v>-3.67</v>
+        <v>-3.56</v>
       </c>
       <c r="P83" s="8">
-        <v>66.33</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="Q83" s="9">
-        <v>-3.67</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>17</v>
@@ -5592,39 +5600,39 @@
         <v>17</v>
       </c>
       <c r="H84" s="8">
-        <v>69.319999999999993</v>
-      </c>
-      <c r="I84" s="10">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="J84" s="10">
-        <v>1.27</v>
+        <v>66.33</v>
+      </c>
+      <c r="I84" s="9">
+        <v>-4.32</v>
+      </c>
+      <c r="J84" s="9">
+        <v>-3.67</v>
       </c>
       <c r="K84" s="8">
-        <v>828.4</v>
+        <v>66.33</v>
       </c>
       <c r="L84" s="9">
-        <v>-0.27</v>
+        <v>-3.67</v>
       </c>
       <c r="M84" s="8">
-        <v>69.319999999999993</v>
-      </c>
-      <c r="N84" s="10">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="O84" s="10">
-        <v>1.27</v>
+        <v>66.33</v>
+      </c>
+      <c r="N84" s="9">
+        <v>-4.32</v>
+      </c>
+      <c r="O84" s="9">
+        <v>-3.67</v>
       </c>
       <c r="P84" s="8">
-        <v>828.4</v>
+        <v>66.33</v>
       </c>
       <c r="Q84" s="9">
-        <v>-0.27</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>17</v>
@@ -5645,39 +5653,39 @@
         <v>17</v>
       </c>
       <c r="H85" s="8">
-        <v>67.680000000000007</v>
-      </c>
-      <c r="I85" s="9">
-        <v>-4.2</v>
-      </c>
-      <c r="J85" s="9">
-        <v>-6.06</v>
+        <v>69.319999999999993</v>
+      </c>
+      <c r="I85" s="10">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="J85" s="10">
+        <v>1.27</v>
       </c>
       <c r="K85" s="8">
-        <v>759.1</v>
+        <v>828.4</v>
       </c>
       <c r="L85" s="9">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
       <c r="M85" s="8">
-        <v>67.680000000000007</v>
-      </c>
-      <c r="N85" s="9">
-        <v>-4.2</v>
-      </c>
-      <c r="O85" s="9">
-        <v>-6.06</v>
+        <v>69.319999999999993</v>
+      </c>
+      <c r="N85" s="10">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="O85" s="10">
+        <v>1.27</v>
       </c>
       <c r="P85" s="8">
-        <v>759.1</v>
+        <v>828.4</v>
       </c>
       <c r="Q85" s="9">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>17</v>
@@ -5698,39 +5706,39 @@
         <v>17</v>
       </c>
       <c r="H86" s="8">
-        <v>70.650000000000006</v>
-      </c>
-      <c r="I86" s="10">
-        <v>1.44</v>
+        <v>67.680000000000007</v>
+      </c>
+      <c r="I86" s="9">
+        <v>-4.2</v>
       </c>
       <c r="J86" s="9">
-        <v>-4.2699999999999996</v>
+        <v>-6.06</v>
       </c>
       <c r="K86" s="8">
-        <v>691.4</v>
-      </c>
-      <c r="L86" s="10">
-        <v>0.17</v>
+        <v>759.1</v>
+      </c>
+      <c r="L86" s="9">
+        <v>-0.41</v>
       </c>
       <c r="M86" s="8">
-        <v>70.650000000000006</v>
-      </c>
-      <c r="N86" s="10">
-        <v>1.44</v>
+        <v>67.680000000000007</v>
+      </c>
+      <c r="N86" s="9">
+        <v>-4.2</v>
       </c>
       <c r="O86" s="9">
-        <v>-4.2699999999999996</v>
+        <v>-6.06</v>
       </c>
       <c r="P86" s="8">
-        <v>691.4</v>
-      </c>
-      <c r="Q86" s="10">
-        <v>0.17</v>
+        <v>759.1</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>17</v>
@@ -5751,39 +5759,39 @@
         <v>17</v>
       </c>
       <c r="H87" s="8">
-        <v>69.64</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="I87" s="10">
-        <v>3.72</v>
+        <v>1.44</v>
       </c>
       <c r="J87" s="9">
-        <v>-4.0199999999999996</v>
+        <v>-4.2699999999999996</v>
       </c>
       <c r="K87" s="8">
-        <v>620.70000000000005</v>
+        <v>691.4</v>
       </c>
       <c r="L87" s="10">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
       <c r="M87" s="8">
-        <v>69.64</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="N87" s="10">
-        <v>3.72</v>
+        <v>1.44</v>
       </c>
       <c r="O87" s="9">
-        <v>-4.0199999999999996</v>
+        <v>-4.2699999999999996</v>
       </c>
       <c r="P87" s="8">
-        <v>620.70000000000005</v>
+        <v>691.4</v>
       </c>
       <c r="Q87" s="10">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5804,39 +5812,39 @@
         <v>17</v>
       </c>
       <c r="H88" s="8">
-        <v>67.14</v>
+        <v>69.64</v>
       </c>
       <c r="I88" s="10">
-        <v>5.72</v>
+        <v>3.72</v>
       </c>
       <c r="J88" s="9">
-        <v>-4.1900000000000004</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="K88" s="8">
-        <v>551.1</v>
+        <v>620.70000000000005</v>
       </c>
       <c r="L88" s="10">
-        <v>1.33</v>
+        <v>0.7</v>
       </c>
       <c r="M88" s="8">
-        <v>67.14</v>
+        <v>69.64</v>
       </c>
       <c r="N88" s="10">
-        <v>5.72</v>
+        <v>3.72</v>
       </c>
       <c r="O88" s="9">
-        <v>-4.1900000000000004</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="P88" s="8">
-        <v>551.1</v>
+        <v>620.70000000000005</v>
       </c>
       <c r="Q88" s="10">
-        <v>1.33</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>17</v>
@@ -5857,39 +5865,39 @@
         <v>17</v>
       </c>
       <c r="H89" s="8">
-        <v>63.51</v>
-      </c>
-      <c r="I89" s="9">
-        <v>-7.64</v>
+        <v>67.14</v>
+      </c>
+      <c r="I89" s="10">
+        <v>5.72</v>
       </c>
       <c r="J89" s="9">
-        <v>-14</v>
+        <v>-4.1900000000000004</v>
       </c>
       <c r="K89" s="8">
-        <v>484</v>
+        <v>551.1</v>
       </c>
       <c r="L89" s="10">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="M89" s="8">
-        <v>63.51</v>
-      </c>
-      <c r="N89" s="9">
-        <v>-7.64</v>
+        <v>67.14</v>
+      </c>
+      <c r="N89" s="10">
+        <v>5.72</v>
       </c>
       <c r="O89" s="9">
-        <v>-14</v>
+        <v>-4.1900000000000004</v>
       </c>
       <c r="P89" s="8">
-        <v>484</v>
+        <v>551.1</v>
       </c>
       <c r="Q89" s="10">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>17</v>
@@ -5910,39 +5918,39 @@
         <v>17</v>
       </c>
       <c r="H90" s="8">
-        <v>68.77</v>
+        <v>63.51</v>
       </c>
       <c r="I90" s="9">
-        <v>-7.16</v>
+        <v>-7.64</v>
       </c>
       <c r="J90" s="9">
-        <v>-10.5</v>
+        <v>-14</v>
       </c>
       <c r="K90" s="8">
-        <v>420.5</v>
+        <v>484</v>
       </c>
       <c r="L90" s="10">
-        <v>5.14</v>
+        <v>2.15</v>
       </c>
       <c r="M90" s="8">
-        <v>68.77</v>
+        <v>63.51</v>
       </c>
       <c r="N90" s="9">
-        <v>-7.16</v>
+        <v>-7.64</v>
       </c>
       <c r="O90" s="9">
-        <v>-10.5</v>
+        <v>-14</v>
       </c>
       <c r="P90" s="8">
-        <v>420.5</v>
+        <v>484</v>
       </c>
       <c r="Q90" s="10">
-        <v>5.14</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>17</v>
@@ -5963,39 +5971,39 @@
         <v>17</v>
       </c>
       <c r="H91" s="8">
-        <v>74.08</v>
-      </c>
-      <c r="I91" s="10">
-        <v>6.5</v>
+        <v>68.77</v>
+      </c>
+      <c r="I91" s="9">
+        <v>-7.16</v>
       </c>
       <c r="J91" s="9">
-        <v>-0.18</v>
+        <v>-10.5</v>
       </c>
       <c r="K91" s="8">
-        <v>351.7</v>
+        <v>420.5</v>
       </c>
       <c r="L91" s="10">
-        <v>8.86</v>
+        <v>5.14</v>
       </c>
       <c r="M91" s="8">
-        <v>74.08</v>
-      </c>
-      <c r="N91" s="10">
-        <v>6.5</v>
+        <v>68.77</v>
+      </c>
+      <c r="N91" s="9">
+        <v>-7.16</v>
       </c>
       <c r="O91" s="9">
-        <v>-0.18</v>
+        <v>-10.5</v>
       </c>
       <c r="P91" s="8">
-        <v>351.7</v>
+        <v>420.5</v>
       </c>
       <c r="Q91" s="10">
-        <v>8.86</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>17</v>
@@ -6016,39 +6024,39 @@
         <v>17</v>
       </c>
       <c r="H92" s="8">
-        <v>69.55</v>
-      </c>
-      <c r="I92" s="9">
-        <v>-6.55</v>
-      </c>
-      <c r="J92" s="10">
-        <v>1.93</v>
+        <v>74.08</v>
+      </c>
+      <c r="I92" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="J92" s="9">
+        <v>-0.18</v>
       </c>
       <c r="K92" s="8">
-        <v>277.60000000000002</v>
+        <v>351.7</v>
       </c>
       <c r="L92" s="10">
-        <v>11.6</v>
+        <v>8.86</v>
       </c>
       <c r="M92" s="8">
-        <v>69.55</v>
-      </c>
-      <c r="N92" s="9">
-        <v>-6.55</v>
-      </c>
-      <c r="O92" s="10">
-        <v>1.93</v>
+        <v>74.08</v>
+      </c>
+      <c r="N92" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="O92" s="9">
+        <v>-0.18</v>
       </c>
       <c r="P92" s="8">
-        <v>277.60000000000002</v>
+        <v>351.7</v>
       </c>
       <c r="Q92" s="10">
-        <v>11.6</v>
+        <v>8.86</v>
       </c>
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6069,39 +6077,39 @@
         <v>17</v>
       </c>
       <c r="H93" s="8">
-        <v>74.430000000000007</v>
-      </c>
-      <c r="I93" s="10">
-        <v>14.9</v>
+        <v>69.55</v>
+      </c>
+      <c r="I93" s="9">
+        <v>-6.55</v>
       </c>
       <c r="J93" s="10">
-        <v>15.2</v>
+        <v>1.93</v>
       </c>
       <c r="K93" s="8">
-        <v>208.1</v>
+        <v>277.60000000000002</v>
       </c>
       <c r="L93" s="10">
-        <v>15.2</v>
+        <v>11.6</v>
       </c>
       <c r="M93" s="8">
-        <v>74.430000000000007</v>
-      </c>
-      <c r="N93" s="10">
-        <v>14.9</v>
+        <v>69.55</v>
+      </c>
+      <c r="N93" s="9">
+        <v>-6.55</v>
       </c>
       <c r="O93" s="10">
-        <v>15.2</v>
+        <v>1.93</v>
       </c>
       <c r="P93" s="8">
-        <v>208.1</v>
+        <v>277.60000000000002</v>
       </c>
       <c r="Q93" s="10">
-        <v>15.2</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6122,31 +6130,31 @@
         <v>17</v>
       </c>
       <c r="H94" s="8">
-        <v>64.760000000000005</v>
-      </c>
-      <c r="I94" s="9">
-        <v>-5.94</v>
+        <v>74.430000000000007</v>
+      </c>
+      <c r="I94" s="10">
+        <v>14.9</v>
       </c>
       <c r="J94" s="10">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="K94" s="8">
-        <v>133.6</v>
+        <v>208.1</v>
       </c>
       <c r="L94" s="10">
         <v>15.2</v>
       </c>
       <c r="M94" s="8">
-        <v>64.760000000000005</v>
-      </c>
-      <c r="N94" s="9">
-        <v>-5.94</v>
+        <v>74.430000000000007</v>
+      </c>
+      <c r="N94" s="10">
+        <v>14.9</v>
       </c>
       <c r="O94" s="10">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="P94" s="8">
-        <v>133.6</v>
+        <v>208.1</v>
       </c>
       <c r="Q94" s="10">
         <v>15.2</v>
@@ -6154,7 +6162,7 @@
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6175,39 +6183,39 @@
         <v>17</v>
       </c>
       <c r="H95" s="8">
-        <v>68.86</v>
-      </c>
-      <c r="I95" s="10">
-        <v>0.59</v>
+        <v>64.760000000000005</v>
+      </c>
+      <c r="I95" s="9">
+        <v>-5.94</v>
       </c>
       <c r="J95" s="10">
-        <v>14.3</v>
+        <v>16.2</v>
       </c>
       <c r="K95" s="8">
-        <v>68.86</v>
+        <v>133.6</v>
       </c>
       <c r="L95" s="10">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="M95" s="8">
-        <v>68.86</v>
-      </c>
-      <c r="N95" s="10">
-        <v>0.59</v>
+        <v>64.760000000000005</v>
+      </c>
+      <c r="N95" s="9">
+        <v>-5.94</v>
       </c>
       <c r="O95" s="10">
-        <v>14.3</v>
+        <v>16.2</v>
       </c>
       <c r="P95" s="8">
-        <v>68.86</v>
+        <v>133.6</v>
       </c>
       <c r="Q95" s="10">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6228,39 +6236,39 @@
         <v>17</v>
       </c>
       <c r="H96" s="8">
-        <v>68.45</v>
-      </c>
-      <c r="I96" s="9">
-        <v>-4.99</v>
+        <v>68.86</v>
+      </c>
+      <c r="I96" s="10">
+        <v>0.59</v>
       </c>
       <c r="J96" s="10">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="K96" s="8">
-        <v>830.7</v>
+        <v>68.86</v>
       </c>
       <c r="L96" s="10">
-        <v>19.8</v>
+        <v>14.3</v>
       </c>
       <c r="M96" s="8">
-        <v>68.45</v>
-      </c>
-      <c r="N96" s="9">
-        <v>-4.99</v>
+        <v>68.86</v>
+      </c>
+      <c r="N96" s="10">
+        <v>0.59</v>
       </c>
       <c r="O96" s="10">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="P96" s="8">
-        <v>830.7</v>
+        <v>68.86</v>
       </c>
       <c r="Q96" s="10">
-        <v>19.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>17</v>
@@ -6281,39 +6289,39 @@
         <v>17</v>
       </c>
       <c r="H97" s="8">
-        <v>72.05</v>
+        <v>68.45</v>
       </c>
       <c r="I97" s="9">
-        <v>-2.38</v>
+        <v>-4.99</v>
       </c>
       <c r="J97" s="10">
-        <v>16.2</v>
+        <v>12.4</v>
       </c>
       <c r="K97" s="8">
-        <v>762.3</v>
+        <v>830.7</v>
       </c>
       <c r="L97" s="10">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="M97" s="8">
-        <v>72.05</v>
+        <v>68.45</v>
       </c>
       <c r="N97" s="9">
-        <v>-2.38</v>
+        <v>-4.99</v>
       </c>
       <c r="O97" s="10">
-        <v>16.2</v>
+        <v>12.4</v>
       </c>
       <c r="P97" s="8">
-        <v>762.3</v>
+        <v>830.7</v>
       </c>
       <c r="Q97" s="10">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>17</v>
@@ -6334,39 +6342,39 @@
         <v>17</v>
       </c>
       <c r="H98" s="8">
-        <v>73.81</v>
-      </c>
-      <c r="I98" s="10">
-        <v>1.72</v>
+        <v>72.05</v>
+      </c>
+      <c r="I98" s="9">
+        <v>-2.38</v>
       </c>
       <c r="J98" s="10">
-        <v>12.6</v>
+        <v>16.2</v>
       </c>
       <c r="K98" s="8">
-        <v>690.2</v>
+        <v>762.3</v>
       </c>
       <c r="L98" s="10">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="M98" s="8">
-        <v>73.81</v>
-      </c>
-      <c r="N98" s="10">
-        <v>1.72</v>
+        <v>72.05</v>
+      </c>
+      <c r="N98" s="9">
+        <v>-2.38</v>
       </c>
       <c r="O98" s="10">
-        <v>12.6</v>
+        <v>16.2</v>
       </c>
       <c r="P98" s="8">
-        <v>690.2</v>
+        <v>762.3</v>
       </c>
       <c r="Q98" s="10">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>17</v>
@@ -6387,39 +6395,39 @@
         <v>17</v>
       </c>
       <c r="H99" s="8">
-        <v>72.56</v>
+        <v>73.81</v>
       </c>
       <c r="I99" s="10">
-        <v>3.53</v>
+        <v>1.72</v>
       </c>
       <c r="J99" s="10">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="K99" s="8">
-        <v>616.4</v>
+        <v>690.2</v>
       </c>
       <c r="L99" s="10">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="M99" s="8">
-        <v>72.56</v>
+        <v>73.81</v>
       </c>
       <c r="N99" s="10">
-        <v>3.53</v>
+        <v>1.72</v>
       </c>
       <c r="O99" s="10">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="P99" s="8">
-        <v>616.4</v>
+        <v>690.2</v>
       </c>
       <c r="Q99" s="10">
-        <v>22</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>41852</v>
+        <v>41883</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>17</v>
@@ -6440,39 +6448,39 @@
         <v>17</v>
       </c>
       <c r="H100" s="8">
-        <v>70.08</v>
-      </c>
-      <c r="I100" s="9">
-        <v>-5.13</v>
+        <v>72.56</v>
+      </c>
+      <c r="I100" s="10">
+        <v>3.53</v>
       </c>
       <c r="J100" s="10">
-        <v>7.65</v>
+        <v>12.5</v>
       </c>
       <c r="K100" s="8">
-        <v>543.79999999999995</v>
+        <v>616.4</v>
       </c>
       <c r="L100" s="10">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="M100" s="8">
-        <v>70.08</v>
-      </c>
-      <c r="N100" s="9">
-        <v>-5.13</v>
+        <v>72.56</v>
+      </c>
+      <c r="N100" s="10">
+        <v>3.53</v>
       </c>
       <c r="O100" s="10">
-        <v>7.65</v>
+        <v>12.5</v>
       </c>
       <c r="P100" s="8">
-        <v>543.79999999999995</v>
+        <v>616.4</v>
       </c>
       <c r="Q100" s="10">
-        <v>23.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>17</v>
@@ -6493,39 +6501,39 @@
         <v>17</v>
       </c>
       <c r="H101" s="8">
-        <v>73.88</v>
+        <v>70.08</v>
       </c>
       <c r="I101" s="9">
-        <v>-3.83</v>
+        <v>-5.13</v>
       </c>
       <c r="J101" s="10">
-        <v>20.5</v>
+        <v>7.65</v>
       </c>
       <c r="K101" s="8">
-        <v>473.8</v>
+        <v>543.79999999999995</v>
       </c>
       <c r="L101" s="10">
-        <v>26.2</v>
+        <v>23.4</v>
       </c>
       <c r="M101" s="8">
-        <v>73.88</v>
+        <v>70.08</v>
       </c>
       <c r="N101" s="9">
-        <v>-3.83</v>
+        <v>-5.13</v>
       </c>
       <c r="O101" s="10">
-        <v>20.5</v>
+        <v>7.65</v>
       </c>
       <c r="P101" s="8">
-        <v>473.8</v>
+        <v>543.79999999999995</v>
       </c>
       <c r="Q101" s="10">
-        <v>26.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>17</v>
@@ -6546,39 +6554,39 @@
         <v>17</v>
       </c>
       <c r="H102" s="8">
-        <v>76.83</v>
-      </c>
-      <c r="I102" s="10">
-        <v>3.51</v>
+        <v>73.88</v>
+      </c>
+      <c r="I102" s="9">
+        <v>-3.83</v>
       </c>
       <c r="J102" s="10">
-        <v>28</v>
+        <v>20.5</v>
       </c>
       <c r="K102" s="8">
-        <v>399.9</v>
+        <v>473.8</v>
       </c>
       <c r="L102" s="10">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="M102" s="8">
-        <v>76.83</v>
-      </c>
-      <c r="N102" s="10">
-        <v>3.51</v>
+        <v>73.88</v>
+      </c>
+      <c r="N102" s="9">
+        <v>-3.83</v>
       </c>
       <c r="O102" s="10">
-        <v>28</v>
+        <v>20.5</v>
       </c>
       <c r="P102" s="8">
-        <v>399.9</v>
+        <v>473.8</v>
       </c>
       <c r="Q102" s="10">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>17</v>
@@ -6599,39 +6607,39 @@
         <v>17</v>
       </c>
       <c r="H103" s="8">
-        <v>74.22</v>
+        <v>76.83</v>
       </c>
       <c r="I103" s="10">
-        <v>8.76</v>
+        <v>3.51</v>
       </c>
       <c r="J103" s="10">
-        <v>24.2</v>
+        <v>28</v>
       </c>
       <c r="K103" s="8">
-        <v>323.10000000000002</v>
+        <v>399.9</v>
       </c>
       <c r="L103" s="10">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="M103" s="8">
-        <v>74.22</v>
+        <v>76.83</v>
       </c>
       <c r="N103" s="10">
-        <v>8.76</v>
+        <v>3.51</v>
       </c>
       <c r="O103" s="10">
-        <v>24.2</v>
+        <v>28</v>
       </c>
       <c r="P103" s="8">
-        <v>323.10000000000002</v>
+        <v>399.9</v>
       </c>
       <c r="Q103" s="10">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>17</v>
@@ -6652,39 +6660,39 @@
         <v>17</v>
       </c>
       <c r="H104" s="8">
-        <v>68.23</v>
+        <v>74.22</v>
       </c>
       <c r="I104" s="10">
-        <v>5.59</v>
+        <v>8.76</v>
       </c>
       <c r="J104" s="10">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
       <c r="K104" s="8">
-        <v>248.8</v>
+        <v>323.10000000000002</v>
       </c>
       <c r="L104" s="10">
-        <v>28</v>
+        <v>27.1</v>
       </c>
       <c r="M104" s="8">
-        <v>68.23</v>
+        <v>74.22</v>
       </c>
       <c r="N104" s="10">
-        <v>5.59</v>
+        <v>8.76</v>
       </c>
       <c r="O104" s="10">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
       <c r="P104" s="8">
-        <v>248.8</v>
+        <v>323.10000000000002</v>
       </c>
       <c r="Q104" s="10">
-        <v>28</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>17</v>
@@ -6705,39 +6713,39 @@
         <v>17</v>
       </c>
       <c r="H105" s="8">
-        <v>64.62</v>
+        <v>68.23</v>
       </c>
       <c r="I105" s="10">
-        <v>15.9</v>
+        <v>5.59</v>
       </c>
       <c r="J105" s="10">
-        <v>30.1</v>
+        <v>21.4</v>
       </c>
       <c r="K105" s="8">
-        <v>180.6</v>
+        <v>248.8</v>
       </c>
       <c r="L105" s="10">
-        <v>30.7</v>
+        <v>28</v>
       </c>
       <c r="M105" s="8">
-        <v>64.62</v>
+        <v>68.23</v>
       </c>
       <c r="N105" s="10">
-        <v>15.9</v>
+        <v>5.59</v>
       </c>
       <c r="O105" s="10">
-        <v>30.1</v>
+        <v>21.4</v>
       </c>
       <c r="P105" s="8">
-        <v>180.6</v>
+        <v>248.8</v>
       </c>
       <c r="Q105" s="10">
-        <v>30.7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>17</v>
@@ -6758,39 +6766,39 @@
         <v>17</v>
       </c>
       <c r="H106" s="8">
-        <v>55.74</v>
-      </c>
-      <c r="I106" s="9">
-        <v>-7.47</v>
+        <v>64.62</v>
+      </c>
+      <c r="I106" s="10">
+        <v>15.9</v>
       </c>
       <c r="J106" s="10">
-        <v>31.1</v>
+        <v>30.1</v>
       </c>
       <c r="K106" s="8">
-        <v>116</v>
+        <v>180.6</v>
       </c>
       <c r="L106" s="10">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="M106" s="8">
-        <v>55.74</v>
-      </c>
-      <c r="N106" s="9">
-        <v>-7.47</v>
+        <v>64.62</v>
+      </c>
+      <c r="N106" s="10">
+        <v>15.9</v>
       </c>
       <c r="O106" s="10">
-        <v>31.1</v>
+        <v>30.1</v>
       </c>
       <c r="P106" s="8">
-        <v>116</v>
+        <v>180.6</v>
       </c>
       <c r="Q106" s="10">
-        <v>31</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>17</v>
@@ -6811,39 +6819,39 @@
         <v>17</v>
       </c>
       <c r="H107" s="8">
-        <v>60.24</v>
+        <v>55.74</v>
       </c>
       <c r="I107" s="9">
-        <v>-1.06</v>
+        <v>-7.47</v>
       </c>
       <c r="J107" s="10">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="K107" s="8">
-        <v>60.24</v>
+        <v>116</v>
       </c>
       <c r="L107" s="10">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="M107" s="8">
-        <v>60.24</v>
+        <v>55.74</v>
       </c>
       <c r="N107" s="9">
-        <v>-1.06</v>
+        <v>-7.47</v>
       </c>
       <c r="O107" s="10">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="P107" s="8">
-        <v>60.24</v>
+        <v>116</v>
       </c>
       <c r="Q107" s="10">
-        <v>30.9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>17</v>
@@ -6864,39 +6872,39 @@
         <v>17</v>
       </c>
       <c r="H108" s="8">
-        <v>60.89</v>
+        <v>60.24</v>
       </c>
       <c r="I108" s="9">
-        <v>-1.77</v>
+        <v>-1.06</v>
       </c>
       <c r="J108" s="10">
-        <v>26.5</v>
+        <v>30.9</v>
       </c>
       <c r="K108" s="8">
-        <v>693.6</v>
+        <v>60.24</v>
       </c>
       <c r="L108" s="10">
-        <v>7.27</v>
+        <v>30.9</v>
       </c>
       <c r="M108" s="8">
-        <v>60.89</v>
+        <v>60.24</v>
       </c>
       <c r="N108" s="9">
-        <v>-1.77</v>
+        <v>-1.06</v>
       </c>
       <c r="O108" s="10">
-        <v>26.5</v>
+        <v>30.9</v>
       </c>
       <c r="P108" s="8">
-        <v>693.6</v>
+        <v>60.24</v>
       </c>
       <c r="Q108" s="10">
-        <v>7.27</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>17</v>
@@ -6917,39 +6925,39 @@
         <v>17</v>
       </c>
       <c r="H109" s="8">
-        <v>61.99</v>
+        <v>60.89</v>
       </c>
       <c r="I109" s="9">
-        <v>-5.42</v>
+        <v>-1.77</v>
       </c>
       <c r="J109" s="10">
-        <v>12.2</v>
+        <v>26.5</v>
       </c>
       <c r="K109" s="8">
-        <v>632.70000000000005</v>
+        <v>693.6</v>
       </c>
       <c r="L109" s="10">
-        <v>5.72</v>
+        <v>7.27</v>
       </c>
       <c r="M109" s="8">
-        <v>61.99</v>
+        <v>60.89</v>
       </c>
       <c r="N109" s="9">
-        <v>-5.42</v>
+        <v>-1.77</v>
       </c>
       <c r="O109" s="10">
-        <v>12.2</v>
+        <v>26.5</v>
       </c>
       <c r="P109" s="8">
-        <v>632.70000000000005</v>
+        <v>693.6</v>
       </c>
       <c r="Q109" s="10">
-        <v>5.72</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>17</v>
@@ -6970,39 +6978,39 @@
         <v>17</v>
       </c>
       <c r="H110" s="8">
-        <v>65.55</v>
-      </c>
-      <c r="I110" s="10">
-        <v>1.6</v>
+        <v>61.99</v>
+      </c>
+      <c r="I110" s="9">
+        <v>-5.42</v>
       </c>
       <c r="J110" s="10">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="K110" s="8">
-        <v>570.70000000000005</v>
+        <v>632.70000000000005</v>
       </c>
       <c r="L110" s="10">
-        <v>5.0599999999999996</v>
+        <v>5.72</v>
       </c>
       <c r="M110" s="8">
-        <v>65.55</v>
-      </c>
-      <c r="N110" s="10">
-        <v>1.6</v>
+        <v>61.99</v>
+      </c>
+      <c r="N110" s="9">
+        <v>-5.42</v>
       </c>
       <c r="O110" s="10">
-        <v>12.9</v>
+        <v>12.2</v>
       </c>
       <c r="P110" s="8">
-        <v>570.70000000000005</v>
+        <v>632.70000000000005</v>
       </c>
       <c r="Q110" s="10">
-        <v>5.0599999999999996</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>17</v>
@@ -7023,39 +7031,39 @@
         <v>17</v>
       </c>
       <c r="H111" s="8">
-        <v>64.510000000000005</v>
-      </c>
-      <c r="I111" s="9">
-        <v>-0.9</v>
+        <v>65.55</v>
+      </c>
+      <c r="I111" s="10">
+        <v>1.6</v>
       </c>
       <c r="J111" s="10">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="K111" s="8">
-        <v>505.1</v>
+        <v>570.70000000000005</v>
       </c>
       <c r="L111" s="10">
-        <v>4.13</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="M111" s="8">
-        <v>64.510000000000005</v>
-      </c>
-      <c r="N111" s="9">
-        <v>-0.9</v>
+        <v>65.55</v>
+      </c>
+      <c r="N111" s="10">
+        <v>1.6</v>
       </c>
       <c r="O111" s="10">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="P111" s="8">
-        <v>505.1</v>
+        <v>570.70000000000005</v>
       </c>
       <c r="Q111" s="10">
-        <v>4.13</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>17</v>
@@ -7076,39 +7084,39 @@
         <v>17</v>
       </c>
       <c r="H112" s="8">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="I112" s="10">
-        <v>6.19</v>
+        <v>64.510000000000005</v>
+      </c>
+      <c r="I112" s="9">
+        <v>-0.9</v>
       </c>
       <c r="J112" s="10">
-        <v>15.3</v>
+        <v>14</v>
       </c>
       <c r="K112" s="8">
-        <v>440.6</v>
+        <v>505.1</v>
       </c>
       <c r="L112" s="10">
-        <v>2.82</v>
+        <v>4.13</v>
       </c>
       <c r="M112" s="8">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="N112" s="10">
-        <v>6.2</v>
+        <v>64.510000000000005</v>
+      </c>
+      <c r="N112" s="9">
+        <v>-0.9</v>
       </c>
       <c r="O112" s="10">
-        <v>15.3</v>
+        <v>14</v>
       </c>
       <c r="P112" s="8">
-        <v>440.6</v>
+        <v>505.1</v>
       </c>
       <c r="Q112" s="10">
-        <v>2.82</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>17</v>
@@ -7129,39 +7137,39 @@
         <v>17</v>
       </c>
       <c r="H113" s="8">
-        <v>61.3</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="I113" s="10">
-        <v>2.13</v>
+        <v>6.19</v>
       </c>
       <c r="J113" s="10">
-        <v>10.6</v>
+        <v>15.3</v>
       </c>
       <c r="K113" s="8">
-        <v>375.5</v>
+        <v>440.6</v>
       </c>
       <c r="L113" s="10">
-        <v>0.93</v>
+        <v>2.82</v>
       </c>
       <c r="M113" s="8">
-        <v>61.3</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="N113" s="10">
-        <v>2.14</v>
+        <v>6.2</v>
       </c>
       <c r="O113" s="10">
-        <v>10.6</v>
+        <v>15.3</v>
       </c>
       <c r="P113" s="8">
-        <v>375.5</v>
+        <v>440.6</v>
       </c>
       <c r="Q113" s="10">
-        <v>0.93</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>17</v>
@@ -7182,39 +7190,39 @@
         <v>17</v>
       </c>
       <c r="H114" s="8">
-        <v>60.02</v>
+        <v>61.3</v>
       </c>
       <c r="I114" s="10">
-        <v>0.4</v>
+        <v>2.13</v>
       </c>
       <c r="J114" s="10">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="K114" s="8">
-        <v>314.2</v>
-      </c>
-      <c r="L114" s="9">
-        <v>-0.76</v>
+        <v>375.5</v>
+      </c>
+      <c r="L114" s="10">
+        <v>0.93</v>
       </c>
       <c r="M114" s="8">
-        <v>60.02</v>
+        <v>61.3</v>
       </c>
       <c r="N114" s="10">
-        <v>0.4</v>
+        <v>2.14</v>
       </c>
       <c r="O114" s="10">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="P114" s="8">
-        <v>314.2</v>
-      </c>
-      <c r="Q114" s="9">
-        <v>-0.77</v>
+        <v>375.5</v>
+      </c>
+      <c r="Q114" s="10">
+        <v>0.93</v>
       </c>
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>17</v>
@@ -7235,39 +7243,39 @@
         <v>17</v>
       </c>
       <c r="H115" s="8">
-        <v>59.78</v>
+        <v>60.02</v>
       </c>
       <c r="I115" s="10">
-        <v>6.33</v>
+        <v>0.4</v>
       </c>
       <c r="J115" s="10">
-        <v>4.4000000000000004</v>
+        <v>11.4</v>
       </c>
       <c r="K115" s="8">
-        <v>254.2</v>
+        <v>314.2</v>
       </c>
       <c r="L115" s="9">
-        <v>-3.25</v>
+        <v>-0.76</v>
       </c>
       <c r="M115" s="8">
-        <v>59.78</v>
+        <v>60.02</v>
       </c>
       <c r="N115" s="10">
-        <v>6.34</v>
+        <v>0.4</v>
       </c>
       <c r="O115" s="10">
-        <v>4.41</v>
+        <v>11.4</v>
       </c>
       <c r="P115" s="8">
-        <v>254.2</v>
+        <v>314.2</v>
       </c>
       <c r="Q115" s="9">
-        <v>-3.26</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>17</v>
@@ -7288,39 +7296,39 @@
         <v>17</v>
       </c>
       <c r="H116" s="8">
-        <v>56.22</v>
+        <v>59.78</v>
       </c>
       <c r="I116" s="10">
-        <v>13.2</v>
+        <v>6.33</v>
       </c>
       <c r="J116" s="10">
-        <v>3.48</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K116" s="8">
-        <v>194.4</v>
+        <v>254.2</v>
       </c>
       <c r="L116" s="9">
-        <v>-5.39</v>
+        <v>-3.25</v>
       </c>
       <c r="M116" s="8">
-        <v>56.22</v>
+        <v>59.78</v>
       </c>
       <c r="N116" s="10">
-        <v>13.2</v>
+        <v>6.34</v>
       </c>
       <c r="O116" s="10">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="P116" s="8">
-        <v>194.4</v>
+        <v>254.2</v>
       </c>
       <c r="Q116" s="9">
-        <v>-5.4</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>17</v>
@@ -7341,39 +7349,39 @@
         <v>17</v>
       </c>
       <c r="H117" s="8">
-        <v>49.66</v>
+        <v>56.22</v>
       </c>
       <c r="I117" s="10">
-        <v>16.8</v>
-      </c>
-      <c r="J117" s="9">
-        <v>-10.3</v>
+        <v>13.2</v>
+      </c>
+      <c r="J117" s="10">
+        <v>3.48</v>
       </c>
       <c r="K117" s="8">
-        <v>138.19999999999999</v>
+        <v>194.4</v>
       </c>
       <c r="L117" s="9">
-        <v>-8.58</v>
+        <v>-5.39</v>
       </c>
       <c r="M117" s="8">
-        <v>49.66</v>
+        <v>56.22</v>
       </c>
       <c r="N117" s="10">
-        <v>16.8</v>
-      </c>
-      <c r="O117" s="9">
-        <v>-10.3</v>
+        <v>13.2</v>
+      </c>
+      <c r="O117" s="10">
+        <v>3.49</v>
       </c>
       <c r="P117" s="8">
-        <v>138.19999999999999</v>
+        <v>194.4</v>
       </c>
       <c r="Q117" s="9">
-        <v>-8.59</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>17</v>
@@ -7394,39 +7402,39 @@
         <v>17</v>
       </c>
       <c r="H118" s="8">
-        <v>42.51</v>
-      </c>
-      <c r="I118" s="9">
-        <v>-7.61</v>
+        <v>49.66</v>
+      </c>
+      <c r="I118" s="10">
+        <v>16.8</v>
       </c>
       <c r="J118" s="9">
-        <v>-9.39</v>
+        <v>-10.3</v>
       </c>
       <c r="K118" s="8">
-        <v>88.53</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="L118" s="9">
-        <v>-7.58</v>
+        <v>-8.58</v>
       </c>
       <c r="M118" s="8">
-        <v>42.51</v>
-      </c>
-      <c r="N118" s="9">
-        <v>-7.62</v>
+        <v>49.66</v>
+      </c>
+      <c r="N118" s="10">
+        <v>16.8</v>
       </c>
       <c r="O118" s="9">
-        <v>-9.4</v>
+        <v>-10.3</v>
       </c>
       <c r="P118" s="8">
-        <v>88.53</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="Q118" s="9">
-        <v>-7.59</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>17</v>
@@ -7447,39 +7455,39 @@
         <v>17</v>
       </c>
       <c r="H119" s="8">
-        <v>46.02</v>
-      </c>
-      <c r="I119" s="8" t="s">
-        <v>17</v>
+        <v>42.51</v>
+      </c>
+      <c r="I119" s="9">
+        <v>-7.61</v>
       </c>
       <c r="J119" s="9">
-        <v>-5.85</v>
+        <v>-9.39</v>
       </c>
       <c r="K119" s="8">
-        <v>46.02</v>
+        <v>88.53</v>
       </c>
       <c r="L119" s="9">
-        <v>-5.85</v>
+        <v>-7.58</v>
       </c>
       <c r="M119" s="8">
-        <v>46.02</v>
+        <v>42.51</v>
       </c>
       <c r="N119" s="9">
-        <v>-4.38</v>
+        <v>-7.62</v>
       </c>
       <c r="O119" s="9">
-        <v>-5.85</v>
+        <v>-9.4</v>
       </c>
       <c r="P119" s="8">
-        <v>46.02</v>
+        <v>88.53</v>
       </c>
       <c r="Q119" s="9">
-        <v>-5.85</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>17</v>
@@ -7500,39 +7508,39 @@
         <v>17</v>
       </c>
       <c r="H120" s="8">
-        <v>41.8</v>
-      </c>
-      <c r="I120" s="9">
-        <v>-13.7</v>
+        <v>46.02</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="J120" s="9">
-        <v>-11</v>
+        <v>-5.85</v>
       </c>
       <c r="K120" s="8">
-        <v>577.1</v>
-      </c>
-      <c r="L120" s="10">
-        <v>2.04</v>
+        <v>46.02</v>
+      </c>
+      <c r="L120" s="9">
+        <v>-5.85</v>
       </c>
       <c r="M120" s="8">
-        <v>48.12</v>
+        <v>46.02</v>
       </c>
       <c r="N120" s="9">
-        <v>-12.9</v>
+        <v>-4.38</v>
       </c>
       <c r="O120" s="9">
-        <v>-5.7</v>
+        <v>-5.85</v>
       </c>
       <c r="P120" s="8">
-        <v>646.5</v>
-      </c>
-      <c r="Q120" s="10">
-        <v>5.58</v>
+        <v>46.02</v>
+      </c>
+      <c r="Q120" s="9">
+        <v>-5.85</v>
       </c>
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>17</v>
@@ -7553,39 +7561,39 @@
         <v>17</v>
       </c>
       <c r="H121" s="8">
-        <v>48.43</v>
+        <v>41.8</v>
       </c>
       <c r="I121" s="9">
-        <v>-5.24</v>
+        <v>-13.7</v>
       </c>
       <c r="J121" s="9">
-        <v>-0.65</v>
+        <v>-11</v>
       </c>
       <c r="K121" s="8">
-        <v>535.29999999999995</v>
+        <v>577.1</v>
       </c>
       <c r="L121" s="10">
-        <v>3.22</v>
+        <v>2.04</v>
       </c>
       <c r="M121" s="8">
-        <v>55.28</v>
+        <v>48.12</v>
       </c>
       <c r="N121" s="9">
-        <v>-4.78</v>
-      </c>
-      <c r="O121" s="10">
-        <v>5.15</v>
+        <v>-12.9</v>
+      </c>
+      <c r="O121" s="9">
+        <v>-5.7</v>
       </c>
       <c r="P121" s="8">
-        <v>598.4</v>
+        <v>646.5</v>
       </c>
       <c r="Q121" s="10">
-        <v>6.61</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>17</v>
@@ -7606,39 +7614,39 @@
         <v>17</v>
       </c>
       <c r="H122" s="8">
-        <v>51.11</v>
-      </c>
-      <c r="I122" s="10">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="J122" s="10">
-        <v>1.61</v>
+        <v>48.43</v>
+      </c>
+      <c r="I122" s="9">
+        <v>-5.24</v>
+      </c>
+      <c r="J122" s="9">
+        <v>-0.65</v>
       </c>
       <c r="K122" s="8">
-        <v>486.9</v>
+        <v>535.29999999999995</v>
       </c>
       <c r="L122" s="10">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="M122" s="8">
-        <v>58.05</v>
-      </c>
-      <c r="N122" s="10">
-        <v>2.62</v>
+        <v>55.28</v>
+      </c>
+      <c r="N122" s="9">
+        <v>-4.78</v>
       </c>
       <c r="O122" s="10">
-        <v>8.5299999999999994</v>
+        <v>5.15</v>
       </c>
       <c r="P122" s="8">
-        <v>543.1</v>
+        <v>598.4</v>
       </c>
       <c r="Q122" s="10">
-        <v>6.76</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>17</v>
@@ -7659,39 +7667,39 @@
         <v>17</v>
       </c>
       <c r="H123" s="8">
-        <v>49.09</v>
-      </c>
-      <c r="I123" s="9">
-        <v>-1.8</v>
-      </c>
-      <c r="J123" s="9">
-        <v>-0.83</v>
+        <v>51.11</v>
+      </c>
+      <c r="I123" s="10">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="J123" s="10">
+        <v>1.61</v>
       </c>
       <c r="K123" s="8">
-        <v>435.8</v>
+        <v>486.9</v>
       </c>
       <c r="L123" s="10">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="M123" s="8">
-        <v>56.57</v>
+        <v>58.05</v>
       </c>
       <c r="N123" s="10">
-        <v>0.18</v>
+        <v>2.62</v>
       </c>
       <c r="O123" s="10">
-        <v>5.96</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="P123" s="8">
-        <v>485.1</v>
+        <v>543.1</v>
       </c>
       <c r="Q123" s="10">
-        <v>6.55</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>17</v>
@@ -7712,39 +7720,39 @@
         <v>17</v>
       </c>
       <c r="H124" s="8">
-        <v>49.99</v>
-      </c>
-      <c r="I124" s="10">
-        <v>0.93</v>
+        <v>49.09</v>
+      </c>
+      <c r="I124" s="9">
+        <v>-1.8</v>
       </c>
       <c r="J124" s="9">
-        <v>-4.8899999999999997</v>
+        <v>-0.83</v>
       </c>
       <c r="K124" s="8">
-        <v>386.7</v>
+        <v>435.8</v>
       </c>
       <c r="L124" s="10">
-        <v>4.49</v>
+        <v>3.86</v>
       </c>
       <c r="M124" s="8">
-        <v>56.47</v>
+        <v>56.57</v>
       </c>
       <c r="N124" s="10">
-        <v>1.91</v>
-      </c>
-      <c r="O124" s="9">
-        <v>-0.41</v>
+        <v>0.18</v>
+      </c>
+      <c r="O124" s="10">
+        <v>5.96</v>
       </c>
       <c r="P124" s="8">
-        <v>428.5</v>
+        <v>485.1</v>
       </c>
       <c r="Q124" s="10">
-        <v>6.63</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>17</v>
@@ -7765,39 +7773,39 @@
         <v>17</v>
       </c>
       <c r="H125" s="8">
-        <v>49.53</v>
+        <v>49.99</v>
       </c>
       <c r="I125" s="10">
-        <v>4.01</v>
-      </c>
-      <c r="J125" s="10">
-        <v>0.77</v>
+        <v>0.93</v>
+      </c>
+      <c r="J125" s="9">
+        <v>-4.8899999999999997</v>
       </c>
       <c r="K125" s="8">
-        <v>336.7</v>
+        <v>386.7</v>
       </c>
       <c r="L125" s="10">
-        <v>6.04</v>
+        <v>4.49</v>
       </c>
       <c r="M125" s="8">
-        <v>55.41</v>
+        <v>56.47</v>
       </c>
       <c r="N125" s="10">
-        <v>2.85</v>
-      </c>
-      <c r="O125" s="10">
-        <v>4.26</v>
+        <v>1.91</v>
+      </c>
+      <c r="O125" s="9">
+        <v>-0.41</v>
       </c>
       <c r="P125" s="8">
-        <v>372</v>
+        <v>428.5</v>
       </c>
       <c r="Q125" s="10">
-        <v>7.78</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>17</v>
@@ -7818,39 +7826,39 @@
         <v>17</v>
       </c>
       <c r="H126" s="8">
-        <v>47.62</v>
-      </c>
-      <c r="I126" s="9">
-        <v>-6.27</v>
+        <v>49.53</v>
+      </c>
+      <c r="I126" s="10">
+        <v>4.01</v>
       </c>
       <c r="J126" s="10">
-        <v>1.3</v>
+        <v>0.77</v>
       </c>
       <c r="K126" s="8">
-        <v>287.10000000000002</v>
+        <v>336.7</v>
       </c>
       <c r="L126" s="10">
-        <v>7.01</v>
+        <v>6.04</v>
       </c>
       <c r="M126" s="8">
-        <v>53.88</v>
-      </c>
-      <c r="N126" s="9">
-        <v>-5.9</v>
+        <v>55.41</v>
+      </c>
+      <c r="N126" s="10">
+        <v>2.85</v>
       </c>
       <c r="O126" s="10">
-        <v>5.68</v>
+        <v>4.26</v>
       </c>
       <c r="P126" s="8">
-        <v>316.60000000000002</v>
+        <v>372</v>
       </c>
       <c r="Q126" s="10">
-        <v>8.43</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>41030</v>
+        <v>41061</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>17</v>
@@ -7871,39 +7879,39 @@
         <v>17</v>
       </c>
       <c r="H127" s="8">
-        <v>50.81</v>
-      </c>
-      <c r="I127" s="10">
-        <v>5.97</v>
+        <v>47.62</v>
+      </c>
+      <c r="I127" s="9">
+        <v>-6.27</v>
       </c>
       <c r="J127" s="10">
-        <v>15.8</v>
+        <v>1.3</v>
       </c>
       <c r="K127" s="8">
-        <v>239.5</v>
+        <v>287.10000000000002</v>
       </c>
       <c r="L127" s="10">
-        <v>8.2200000000000006</v>
+        <v>7.01</v>
       </c>
       <c r="M127" s="8">
-        <v>57.25</v>
-      </c>
-      <c r="N127" s="10">
-        <v>5.4</v>
+        <v>53.88</v>
+      </c>
+      <c r="N127" s="9">
+        <v>-5.9</v>
       </c>
       <c r="O127" s="10">
-        <v>18</v>
+        <v>5.68</v>
       </c>
       <c r="P127" s="8">
-        <v>262.8</v>
+        <v>316.60000000000002</v>
       </c>
       <c r="Q127" s="10">
-        <v>9.01</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>41000</v>
+        <v>41030</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>17</v>
@@ -7924,39 +7932,39 @@
         <v>17</v>
       </c>
       <c r="H128" s="8">
-        <v>47.94</v>
-      </c>
-      <c r="I128" s="9">
-        <v>-4.9800000000000004</v>
+        <v>50.81</v>
+      </c>
+      <c r="I128" s="10">
+        <v>5.97</v>
       </c>
       <c r="J128" s="10">
-        <v>8.1300000000000008</v>
+        <v>15.8</v>
       </c>
       <c r="K128" s="8">
-        <v>188.7</v>
+        <v>239.5</v>
       </c>
       <c r="L128" s="10">
-        <v>6.35</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="M128" s="8">
-        <v>54.32</v>
-      </c>
-      <c r="N128" s="9">
-        <v>-1.91</v>
+        <v>57.25</v>
+      </c>
+      <c r="N128" s="10">
+        <v>5.4</v>
       </c>
       <c r="O128" s="10">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="P128" s="8">
-        <v>205.5</v>
+        <v>262.8</v>
       </c>
       <c r="Q128" s="10">
-        <v>6.74</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>40969</v>
+        <v>41000</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>17</v>
@@ -7977,39 +7985,39 @@
         <v>17</v>
       </c>
       <c r="H129" s="8">
-        <v>50.45</v>
-      </c>
-      <c r="I129" s="10">
-        <v>15.3</v>
+        <v>47.94</v>
+      </c>
+      <c r="I129" s="9">
+        <v>-4.9800000000000004</v>
       </c>
       <c r="J129" s="10">
-        <v>9.51</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="K129" s="8">
-        <v>140.80000000000001</v>
+        <v>188.7</v>
       </c>
       <c r="L129" s="10">
-        <v>5.76</v>
+        <v>6.35</v>
       </c>
       <c r="M129" s="8">
-        <v>55.38</v>
-      </c>
-      <c r="N129" s="10">
-        <v>18</v>
+        <v>54.32</v>
+      </c>
+      <c r="N129" s="9">
+        <v>-1.91</v>
       </c>
       <c r="O129" s="10">
-        <v>9.85</v>
+        <v>13.5</v>
       </c>
       <c r="P129" s="8">
-        <v>151.19999999999999</v>
+        <v>205.5</v>
       </c>
       <c r="Q129" s="10">
-        <v>4.5</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>40940</v>
+        <v>40969</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>17</v>
@@ -8030,39 +8038,39 @@
         <v>17</v>
       </c>
       <c r="H130" s="8">
-        <v>43.76</v>
-      </c>
-      <c r="I130" s="9">
-        <v>-6.01</v>
+        <v>50.45</v>
+      </c>
+      <c r="I130" s="10">
+        <v>15.3</v>
       </c>
       <c r="J130" s="10">
-        <v>7.16</v>
+        <v>9.51</v>
       </c>
       <c r="K130" s="8">
-        <v>90.32</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="L130" s="10">
-        <v>3.78</v>
+        <v>5.76</v>
       </c>
       <c r="M130" s="8">
-        <v>46.92</v>
-      </c>
-      <c r="N130" s="9">
-        <v>-4.01</v>
+        <v>55.38</v>
+      </c>
+      <c r="N130" s="10">
+        <v>18</v>
       </c>
       <c r="O130" s="10">
-        <v>6.26</v>
+        <v>9.85</v>
       </c>
       <c r="P130" s="8">
-        <v>95.8</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="Q130" s="10">
-        <v>1.63</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>40909</v>
+        <v>40940</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>17</v>
@@ -8083,39 +8091,39 @@
         <v>17</v>
       </c>
       <c r="H131" s="8">
-        <v>46.56</v>
+        <v>43.76</v>
       </c>
       <c r="I131" s="9">
-        <v>-0.81</v>
+        <v>-6.01</v>
       </c>
       <c r="J131" s="10">
-        <v>0.79</v>
+        <v>7.16</v>
       </c>
       <c r="K131" s="8">
-        <v>46.56</v>
+        <v>90.32</v>
       </c>
       <c r="L131" s="10">
-        <v>0.79</v>
+        <v>3.78</v>
       </c>
       <c r="M131" s="8">
-        <v>48.88</v>
+        <v>46.92</v>
       </c>
       <c r="N131" s="9">
-        <v>-4.2300000000000004</v>
-      </c>
-      <c r="O131" s="9">
-        <v>-2.4500000000000002</v>
+        <v>-4.01</v>
+      </c>
+      <c r="O131" s="10">
+        <v>6.26</v>
       </c>
       <c r="P131" s="8">
-        <v>48.88</v>
-      </c>
-      <c r="Q131" s="9">
-        <v>-2.4500000000000002</v>
+        <v>95.8</v>
+      </c>
+      <c r="Q131" s="10">
+        <v>1.63</v>
       </c>
     </row>
     <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>40878</v>
+        <v>40909</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>17</v>
@@ -8136,39 +8144,39 @@
         <v>17</v>
       </c>
       <c r="H132" s="8">
-        <v>46.94</v>
+        <v>46.56</v>
       </c>
       <c r="I132" s="9">
-        <v>-3.71</v>
-      </c>
-      <c r="J132" s="9">
-        <v>-2.65</v>
+        <v>-0.81</v>
+      </c>
+      <c r="J132" s="10">
+        <v>0.79</v>
       </c>
       <c r="K132" s="8">
-        <v>565.5</v>
-      </c>
-      <c r="L132" s="9">
-        <v>-5.85</v>
+        <v>46.56</v>
+      </c>
+      <c r="L132" s="10">
+        <v>0.79</v>
       </c>
       <c r="M132" s="8">
-        <v>51.03</v>
+        <v>48.88</v>
       </c>
       <c r="N132" s="9">
-        <v>-2.92</v>
+        <v>-4.2300000000000004</v>
       </c>
       <c r="O132" s="9">
-        <v>-3.87</v>
+        <v>-2.4500000000000002</v>
       </c>
       <c r="P132" s="8">
-        <v>612.4</v>
+        <v>48.88</v>
       </c>
       <c r="Q132" s="9">
-        <v>-4.0999999999999996</v>
+        <v>-2.4500000000000002</v>
       </c>
     </row>
     <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>40848</v>
+        <v>40878</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>17</v>
@@ -8189,39 +8197,39 @@
         <v>17</v>
       </c>
       <c r="H133" s="8">
-        <v>48.75</v>
+        <v>46.94</v>
       </c>
       <c r="I133" s="9">
-        <v>-3.07</v>
-      </c>
-      <c r="J133" s="10">
-        <v>3.82</v>
+        <v>-3.71</v>
+      </c>
+      <c r="J133" s="9">
+        <v>-2.65</v>
       </c>
       <c r="K133" s="8">
-        <v>518.6</v>
+        <v>565.5</v>
       </c>
       <c r="L133" s="9">
-        <v>-6.13</v>
+        <v>-5.85</v>
       </c>
       <c r="M133" s="8">
-        <v>52.57</v>
+        <v>51.03</v>
       </c>
       <c r="N133" s="9">
-        <v>-1.72</v>
-      </c>
-      <c r="O133" s="10">
-        <v>2.38</v>
+        <v>-2.92</v>
+      </c>
+      <c r="O133" s="9">
+        <v>-3.87</v>
       </c>
       <c r="P133" s="8">
-        <v>561.29999999999995</v>
+        <v>612.4</v>
       </c>
       <c r="Q133" s="9">
-        <v>-4.12</v>
+        <v>-4.0999999999999996</v>
       </c>
     </row>
     <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>40817</v>
+        <v>40848</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>17</v>
@@ -8242,39 +8250,39 @@
         <v>17</v>
       </c>
       <c r="H134" s="8">
-        <v>50.3</v>
-      </c>
-      <c r="I134" s="10">
-        <v>1.6</v>
+        <v>48.75</v>
+      </c>
+      <c r="I134" s="9">
+        <v>-3.07</v>
       </c>
       <c r="J134" s="10">
-        <v>8.08</v>
+        <v>3.82</v>
       </c>
       <c r="K134" s="8">
-        <v>469.8</v>
+        <v>518.6</v>
       </c>
       <c r="L134" s="9">
-        <v>-7.06</v>
+        <v>-6.13</v>
       </c>
       <c r="M134" s="8">
-        <v>53.49</v>
-      </c>
-      <c r="N134" s="10">
-        <v>0.19</v>
+        <v>52.57</v>
+      </c>
+      <c r="N134" s="9">
+        <v>-1.72</v>
       </c>
       <c r="O134" s="10">
-        <v>6.24</v>
+        <v>2.38</v>
       </c>
       <c r="P134" s="8">
-        <v>508.8</v>
+        <v>561.29999999999995</v>
       </c>
       <c r="Q134" s="9">
-        <v>-4.75</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>40787</v>
+        <v>40817</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>17</v>
@@ -8295,39 +8303,39 @@
         <v>17</v>
       </c>
       <c r="H135" s="8">
-        <v>49.5</v>
-      </c>
-      <c r="I135" s="9">
-        <v>-5.83</v>
+        <v>50.3</v>
+      </c>
+      <c r="I135" s="10">
+        <v>1.6</v>
       </c>
       <c r="J135" s="10">
-        <v>2.09</v>
+        <v>8.08</v>
       </c>
       <c r="K135" s="8">
-        <v>419.5</v>
+        <v>469.8</v>
       </c>
       <c r="L135" s="9">
-        <v>-8.59</v>
+        <v>-7.06</v>
       </c>
       <c r="M135" s="8">
-        <v>53.39</v>
-      </c>
-      <c r="N135" s="9">
-        <v>-5.84</v>
+        <v>53.49</v>
+      </c>
+      <c r="N135" s="10">
+        <v>0.19</v>
       </c>
       <c r="O135" s="10">
-        <v>2.37</v>
+        <v>6.24</v>
       </c>
       <c r="P135" s="8">
-        <v>455.3</v>
+        <v>508.8</v>
       </c>
       <c r="Q135" s="9">
-        <v>-5.89</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>40756</v>
+        <v>40787</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>17</v>
@@ -8348,39 +8356,39 @@
         <v>17</v>
       </c>
       <c r="H136" s="8">
-        <v>52.57</v>
-      </c>
-      <c r="I136" s="10">
-        <v>6.95</v>
+        <v>49.5</v>
+      </c>
+      <c r="I136" s="9">
+        <v>-5.83</v>
       </c>
       <c r="J136" s="10">
-        <v>1.22</v>
+        <v>2.09</v>
       </c>
       <c r="K136" s="8">
-        <v>370</v>
+        <v>419.5</v>
       </c>
       <c r="L136" s="9">
-        <v>-9.86</v>
+        <v>-8.59</v>
       </c>
       <c r="M136" s="8">
-        <v>56.71</v>
-      </c>
-      <c r="N136" s="10">
-        <v>6.69</v>
+        <v>53.39</v>
+      </c>
+      <c r="N136" s="9">
+        <v>-5.84</v>
       </c>
       <c r="O136" s="10">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="P136" s="8">
-        <v>401.9</v>
+        <v>455.3</v>
       </c>
       <c r="Q136" s="9">
-        <v>-6.89</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>40725</v>
+        <v>40756</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>17</v>
@@ -8401,39 +8409,39 @@
         <v>17</v>
       </c>
       <c r="H137" s="8">
-        <v>49.15</v>
+        <v>52.57</v>
       </c>
       <c r="I137" s="10">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="J137" s="9">
-        <v>-5.54</v>
+        <v>6.95</v>
+      </c>
+      <c r="J137" s="10">
+        <v>1.22</v>
       </c>
       <c r="K137" s="8">
-        <v>317.5</v>
+        <v>370</v>
       </c>
       <c r="L137" s="9">
-        <v>-11.5</v>
+        <v>-9.86</v>
       </c>
       <c r="M137" s="8">
-        <v>53.15</v>
+        <v>56.71</v>
       </c>
       <c r="N137" s="10">
-        <v>4.25</v>
-      </c>
-      <c r="O137" s="9">
-        <v>-3.65</v>
+        <v>6.69</v>
+      </c>
+      <c r="O137" s="10">
+        <v>1.78</v>
       </c>
       <c r="P137" s="8">
-        <v>345.2</v>
+        <v>401.9</v>
       </c>
       <c r="Q137" s="9">
-        <v>-8.18</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>40695</v>
+        <v>40725</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>17</v>
@@ -8454,39 +8462,39 @@
         <v>17</v>
       </c>
       <c r="H138" s="8">
-        <v>47.01</v>
+        <v>49.15</v>
       </c>
       <c r="I138" s="10">
-        <v>7.11</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="J138" s="9">
-        <v>-9.52</v>
+        <v>-5.54</v>
       </c>
       <c r="K138" s="8">
-        <v>268.3</v>
+        <v>317.5</v>
       </c>
       <c r="L138" s="9">
-        <v>-12.5</v>
+        <v>-11.5</v>
       </c>
       <c r="M138" s="8">
-        <v>50.98</v>
+        <v>53.15</v>
       </c>
       <c r="N138" s="10">
-        <v>5.08</v>
+        <v>4.25</v>
       </c>
       <c r="O138" s="9">
-        <v>-6.8</v>
+        <v>-3.65</v>
       </c>
       <c r="P138" s="8">
-        <v>292</v>
+        <v>345.2</v>
       </c>
       <c r="Q138" s="9">
-        <v>-8.9600000000000009</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>40664</v>
+        <v>40695</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>17</v>
@@ -8507,39 +8515,39 @@
         <v>17</v>
       </c>
       <c r="H139" s="8">
-        <v>43.88</v>
-      </c>
-      <c r="I139" s="9">
-        <v>-1.02</v>
+        <v>47.01</v>
+      </c>
+      <c r="I139" s="10">
+        <v>7.11</v>
       </c>
       <c r="J139" s="9">
-        <v>-17.3</v>
+        <v>-9.52</v>
       </c>
       <c r="K139" s="8">
-        <v>221.3</v>
+        <v>268.3</v>
       </c>
       <c r="L139" s="9">
-        <v>-13.1</v>
+        <v>-12.5</v>
       </c>
       <c r="M139" s="8">
-        <v>48.52</v>
+        <v>50.98</v>
       </c>
       <c r="N139" s="10">
-        <v>1.38</v>
+        <v>5.08</v>
       </c>
       <c r="O139" s="9">
-        <v>-12.4</v>
+        <v>-6.8</v>
       </c>
       <c r="P139" s="8">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="Q139" s="9">
-        <v>-9.4</v>
+        <v>-8.9600000000000009</v>
       </c>
     </row>
     <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>40634</v>
+        <v>40664</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>17</v>
@@ -8560,39 +8568,39 @@
         <v>17</v>
       </c>
       <c r="H140" s="8">
-        <v>44.33</v>
+        <v>43.88</v>
       </c>
       <c r="I140" s="9">
-        <v>-3.77</v>
+        <v>-1.02</v>
       </c>
       <c r="J140" s="9">
+        <v>-17.3</v>
+      </c>
+      <c r="K140" s="8">
+        <v>221.3</v>
+      </c>
+      <c r="L140" s="9">
         <v>-13.1</v>
       </c>
-      <c r="K140" s="8">
-        <v>177.4</v>
-      </c>
-      <c r="L140" s="9">
-        <v>-12</v>
-      </c>
       <c r="M140" s="8">
-        <v>47.86</v>
-      </c>
-      <c r="N140" s="9">
-        <v>-5.07</v>
+        <v>48.52</v>
+      </c>
+      <c r="N140" s="10">
+        <v>1.38</v>
       </c>
       <c r="O140" s="9">
-        <v>-11</v>
+        <v>-12.4</v>
       </c>
       <c r="P140" s="8">
-        <v>192.5</v>
+        <v>241</v>
       </c>
       <c r="Q140" s="9">
-        <v>-8.6199999999999992</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>40603</v>
+        <v>40634</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>17</v>
@@ -8613,39 +8621,39 @@
         <v>17</v>
       </c>
       <c r="H141" s="8">
-        <v>46.07</v>
-      </c>
-      <c r="I141" s="10">
-        <v>12.8</v>
+        <v>44.33</v>
+      </c>
+      <c r="I141" s="9">
+        <v>-3.77</v>
       </c>
       <c r="J141" s="9">
-        <v>-12.4</v>
+        <v>-13.1</v>
       </c>
       <c r="K141" s="8">
-        <v>133.1</v>
+        <v>177.4</v>
       </c>
       <c r="L141" s="9">
-        <v>-11.6</v>
+        <v>-12</v>
       </c>
       <c r="M141" s="8">
-        <v>50.41</v>
-      </c>
-      <c r="N141" s="10">
-        <v>14.2</v>
+        <v>47.86</v>
+      </c>
+      <c r="N141" s="9">
+        <v>-5.07</v>
       </c>
       <c r="O141" s="9">
-        <v>-8.5399999999999991</v>
+        <v>-11</v>
       </c>
       <c r="P141" s="8">
-        <v>144.69999999999999</v>
+        <v>192.5</v>
       </c>
       <c r="Q141" s="9">
-        <v>-7.79</v>
+        <v>-8.6199999999999992</v>
       </c>
     </row>
     <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>40575</v>
+        <v>40603</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>17</v>
@@ -8666,39 +8674,39 @@
         <v>17</v>
       </c>
       <c r="H142" s="8">
-        <v>40.83</v>
-      </c>
-      <c r="I142" s="9">
+        <v>46.07</v>
+      </c>
+      <c r="I142" s="10">
+        <v>12.8</v>
+      </c>
+      <c r="J142" s="9">
+        <v>-12.4</v>
+      </c>
+      <c r="K142" s="8">
+        <v>133.1</v>
+      </c>
+      <c r="L142" s="9">
         <v>-11.6</v>
       </c>
-      <c r="J142" s="9">
-        <v>-13.3</v>
-      </c>
-      <c r="K142" s="8">
-        <v>87.03</v>
-      </c>
-      <c r="L142" s="9">
-        <v>-11.1</v>
-      </c>
       <c r="M142" s="8">
-        <v>44.15</v>
-      </c>
-      <c r="N142" s="9">
-        <v>-11.9</v>
+        <v>50.41</v>
+      </c>
+      <c r="N142" s="10">
+        <v>14.2</v>
       </c>
       <c r="O142" s="9">
-        <v>-9.32</v>
+        <v>-8.5399999999999991</v>
       </c>
       <c r="P142" s="8">
-        <v>94.26</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="Q142" s="9">
-        <v>-7.38</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>40544</v>
+        <v>40575</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>17</v>
@@ -8719,39 +8727,39 @@
         <v>17</v>
       </c>
       <c r="H143" s="8">
-        <v>46.19</v>
+        <v>40.83</v>
       </c>
       <c r="I143" s="9">
-        <v>-4.2</v>
+        <v>-11.6</v>
       </c>
       <c r="J143" s="9">
-        <v>-9.11</v>
+        <v>-13.3</v>
       </c>
       <c r="K143" s="8">
-        <v>46.19</v>
+        <v>87.03</v>
       </c>
       <c r="L143" s="9">
-        <v>-9.11</v>
+        <v>-11.1</v>
       </c>
       <c r="M143" s="8">
-        <v>50.11</v>
+        <v>44.15</v>
       </c>
       <c r="N143" s="9">
-        <v>-5.62</v>
+        <v>-11.9</v>
       </c>
       <c r="O143" s="9">
-        <v>-5.59</v>
+        <v>-9.32</v>
       </c>
       <c r="P143" s="8">
-        <v>50.11</v>
+        <v>94.26</v>
       </c>
       <c r="Q143" s="9">
-        <v>-5.59</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>40513</v>
+        <v>40544</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>17</v>
@@ -8772,39 +8780,39 @@
         <v>17</v>
       </c>
       <c r="H144" s="8">
-        <v>48.22</v>
-      </c>
-      <c r="I144" s="10">
-        <v>2.68</v>
+        <v>46.19</v>
+      </c>
+      <c r="I144" s="9">
+        <v>-4.2</v>
       </c>
       <c r="J144" s="9">
-        <v>-9.75</v>
+        <v>-9.11</v>
       </c>
       <c r="K144" s="8">
-        <v>600.70000000000005</v>
-      </c>
-      <c r="L144" s="10">
-        <v>5.6</v>
+        <v>46.19</v>
+      </c>
+      <c r="L144" s="9">
+        <v>-9.11</v>
       </c>
       <c r="M144" s="8">
-        <v>53.09</v>
-      </c>
-      <c r="N144" s="10">
-        <v>3.39</v>
+        <v>50.11</v>
+      </c>
+      <c r="N144" s="9">
+        <v>-5.62</v>
       </c>
       <c r="O144" s="9">
-        <v>-4.8899999999999997</v>
+        <v>-5.59</v>
       </c>
       <c r="P144" s="8">
-        <v>638.6</v>
-      </c>
-      <c r="Q144" s="10">
-        <v>7.7</v>
+        <v>50.11</v>
+      </c>
+      <c r="Q144" s="9">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>40483</v>
+        <v>40513</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>17</v>
@@ -8825,39 +8833,39 @@
         <v>17</v>
       </c>
       <c r="H145" s="8">
-        <v>46.96</v>
+        <v>48.22</v>
       </c>
       <c r="I145" s="10">
-        <v>0.9</v>
+        <v>2.68</v>
       </c>
       <c r="J145" s="9">
-        <v>-14.3</v>
+        <v>-9.75</v>
       </c>
       <c r="K145" s="8">
-        <v>552.5</v>
+        <v>600.70000000000005</v>
       </c>
       <c r="L145" s="10">
-        <v>7.19</v>
+        <v>5.6</v>
       </c>
       <c r="M145" s="8">
-        <v>51.35</v>
+        <v>53.09</v>
       </c>
       <c r="N145" s="10">
-        <v>1.99</v>
+        <v>3.39</v>
       </c>
       <c r="O145" s="9">
-        <v>-10.199999999999999</v>
+        <v>-4.8899999999999997</v>
       </c>
       <c r="P145" s="8">
-        <v>585.5</v>
+        <v>638.6</v>
       </c>
       <c r="Q145" s="10">
-        <v>9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>40452</v>
+        <v>40483</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>17</v>
@@ -8878,39 +8886,39 @@
         <v>17</v>
       </c>
       <c r="H146" s="8">
-        <v>46.54</v>
-      </c>
-      <c r="I146" s="9">
-        <v>-4.0199999999999996</v>
+        <v>46.96</v>
+      </c>
+      <c r="I146" s="10">
+        <v>0.9</v>
       </c>
       <c r="J146" s="9">
-        <v>-22.3</v>
+        <v>-14.3</v>
       </c>
       <c r="K146" s="8">
-        <v>505.5</v>
+        <v>552.5</v>
       </c>
       <c r="L146" s="10">
-        <v>9.75</v>
+        <v>7.19</v>
       </c>
       <c r="M146" s="8">
-        <v>50.35</v>
-      </c>
-      <c r="N146" s="9">
-        <v>-3.46</v>
+        <v>51.35</v>
+      </c>
+      <c r="N146" s="10">
+        <v>1.99</v>
       </c>
       <c r="O146" s="9">
-        <v>-19.100000000000001</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="P146" s="8">
-        <v>534.1</v>
+        <v>585.5</v>
       </c>
       <c r="Q146" s="10">
-        <v>11.3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>40422</v>
+        <v>40452</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>17</v>
@@ -8931,39 +8939,39 @@
         <v>17</v>
       </c>
       <c r="H147" s="8">
-        <v>48.49</v>
+        <v>46.54</v>
       </c>
       <c r="I147" s="9">
-        <v>-6.62</v>
+        <v>-4.0199999999999996</v>
       </c>
       <c r="J147" s="9">
-        <v>-18.899999999999999</v>
+        <v>-22.3</v>
       </c>
       <c r="K147" s="8">
-        <v>459</v>
+        <v>505.5</v>
       </c>
       <c r="L147" s="10">
-        <v>14.5</v>
+        <v>9.75</v>
       </c>
       <c r="M147" s="8">
-        <v>52.15</v>
+        <v>50.35</v>
       </c>
       <c r="N147" s="9">
-        <v>-6.39</v>
+        <v>-3.46</v>
       </c>
       <c r="O147" s="9">
-        <v>-16.399999999999999</v>
+        <v>-19.100000000000001</v>
       </c>
       <c r="P147" s="8">
-        <v>483.8</v>
+        <v>534.1</v>
       </c>
       <c r="Q147" s="10">
-        <v>15.8</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>40391</v>
+        <v>40422</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>17</v>
@@ -8984,39 +8992,39 @@
         <v>17</v>
       </c>
       <c r="H148" s="8">
-        <v>51.93</v>
+        <v>48.49</v>
       </c>
       <c r="I148" s="9">
-        <v>-0.2</v>
+        <v>-6.62</v>
       </c>
       <c r="J148" s="9">
-        <v>-7.1</v>
+        <v>-18.899999999999999</v>
       </c>
       <c r="K148" s="8">
-        <v>410.5</v>
+        <v>459</v>
       </c>
       <c r="L148" s="10">
-        <v>20.399999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="M148" s="8">
-        <v>55.72</v>
-      </c>
-      <c r="N148" s="10">
-        <v>1</v>
+        <v>52.15</v>
+      </c>
+      <c r="N148" s="9">
+        <v>-6.39</v>
       </c>
       <c r="O148" s="9">
-        <v>-4.4000000000000004</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="P148" s="8">
-        <v>431.6</v>
+        <v>483.8</v>
       </c>
       <c r="Q148" s="10">
-        <v>21.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>40360</v>
+        <v>40391</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>17</v>
@@ -9037,39 +9045,39 @@
         <v>17</v>
       </c>
       <c r="H149" s="8">
-        <v>52.04</v>
-      </c>
-      <c r="I149" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="J149" s="10">
-        <v>0.76</v>
+        <v>51.93</v>
+      </c>
+      <c r="I149" s="9">
+        <v>-0.2</v>
+      </c>
+      <c r="J149" s="9">
+        <v>-7.1</v>
       </c>
       <c r="K149" s="8">
-        <v>358.6</v>
+        <v>410.5</v>
       </c>
       <c r="L149" s="10">
-        <v>25.8</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M149" s="8">
-        <v>55.16</v>
+        <v>55.72</v>
       </c>
       <c r="N149" s="10">
-        <v>0.85</v>
-      </c>
-      <c r="O149" s="10">
-        <v>2.14</v>
+        <v>1</v>
+      </c>
+      <c r="O149" s="9">
+        <v>-4.4000000000000004</v>
       </c>
       <c r="P149" s="8">
-        <v>375.9</v>
+        <v>431.6</v>
       </c>
       <c r="Q149" s="10">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>40330</v>
+        <v>40360</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>17</v>
@@ -9090,39 +9098,39 @@
         <v>17</v>
       </c>
       <c r="H150" s="8">
-        <v>51.96</v>
-      </c>
-      <c r="I150" s="9">
-        <v>-2.09</v>
+        <v>52.04</v>
+      </c>
+      <c r="I150" s="10">
+        <v>0.15</v>
       </c>
       <c r="J150" s="10">
-        <v>1.73</v>
+        <v>0.76</v>
       </c>
       <c r="K150" s="8">
-        <v>306.60000000000002</v>
+        <v>358.6</v>
       </c>
       <c r="L150" s="10">
-        <v>31.3</v>
+        <v>25.8</v>
       </c>
       <c r="M150" s="8">
-        <v>54.7</v>
-      </c>
-      <c r="N150" s="9">
-        <v>-1.22</v>
+        <v>55.16</v>
+      </c>
+      <c r="N150" s="10">
+        <v>0.85</v>
       </c>
       <c r="O150" s="10">
-        <v>2.83</v>
+        <v>2.14</v>
       </c>
       <c r="P150" s="8">
-        <v>320.8</v>
+        <v>375.9</v>
       </c>
       <c r="Q150" s="10">
-        <v>32</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>40299</v>
+        <v>40330</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>17</v>
@@ -9143,39 +9151,39 @@
         <v>17</v>
       </c>
       <c r="H151" s="8">
-        <v>53.07</v>
-      </c>
-      <c r="I151" s="10">
-        <v>4.0199999999999996</v>
+        <v>51.96</v>
+      </c>
+      <c r="I151" s="9">
+        <v>-2.09</v>
       </c>
       <c r="J151" s="10">
-        <v>9.9</v>
+        <v>1.73</v>
       </c>
       <c r="K151" s="8">
-        <v>254.6</v>
+        <v>306.60000000000002</v>
       </c>
       <c r="L151" s="10">
-        <v>39.6</v>
+        <v>31.3</v>
       </c>
       <c r="M151" s="8">
-        <v>55.37</v>
-      </c>
-      <c r="N151" s="10">
-        <v>2.94</v>
+        <v>54.7</v>
+      </c>
+      <c r="N151" s="9">
+        <v>-1.22</v>
       </c>
       <c r="O151" s="10">
-        <v>10.9</v>
+        <v>2.83</v>
       </c>
       <c r="P151" s="8">
-        <v>266.10000000000002</v>
+        <v>320.8</v>
       </c>
       <c r="Q151" s="10">
-        <v>40.200000000000003</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>40269</v>
+        <v>40299</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>17</v>
@@ -9196,39 +9204,39 @@
         <v>17</v>
       </c>
       <c r="H152" s="8">
-        <v>51.01</v>
-      </c>
-      <c r="I152" s="9">
-        <v>-2.96</v>
+        <v>53.07</v>
+      </c>
+      <c r="I152" s="10">
+        <v>4.0199999999999996</v>
       </c>
       <c r="J152" s="10">
-        <v>21.4</v>
+        <v>9.9</v>
       </c>
       <c r="K152" s="8">
-        <v>201.5</v>
+        <v>254.6</v>
       </c>
       <c r="L152" s="10">
-        <v>50.3</v>
+        <v>39.6</v>
       </c>
       <c r="M152" s="8">
-        <v>53.79</v>
-      </c>
-      <c r="N152" s="9">
-        <v>-2.41</v>
+        <v>55.37</v>
+      </c>
+      <c r="N152" s="10">
+        <v>2.94</v>
       </c>
       <c r="O152" s="10">
-        <v>23.2</v>
+        <v>10.9</v>
       </c>
       <c r="P152" s="8">
-        <v>210.7</v>
+        <v>266.10000000000002</v>
       </c>
       <c r="Q152" s="10">
-        <v>50.6</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>40238</v>
+        <v>40269</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>17</v>
@@ -9249,39 +9257,39 @@
         <v>17</v>
       </c>
       <c r="H153" s="8">
-        <v>52.57</v>
-      </c>
-      <c r="I153" s="10">
-        <v>11.6</v>
+        <v>51.01</v>
+      </c>
+      <c r="I153" s="9">
+        <v>-2.96</v>
       </c>
       <c r="J153" s="10">
-        <v>35.9</v>
+        <v>21.4</v>
       </c>
       <c r="K153" s="8">
-        <v>150.5</v>
+        <v>201.5</v>
       </c>
       <c r="L153" s="10">
-        <v>63.5</v>
+        <v>50.3</v>
       </c>
       <c r="M153" s="8">
-        <v>55.12</v>
-      </c>
-      <c r="N153" s="10">
-        <v>13.2</v>
+        <v>53.79</v>
+      </c>
+      <c r="N153" s="9">
+        <v>-2.41</v>
       </c>
       <c r="O153" s="10">
-        <v>34.200000000000003</v>
+        <v>23.2</v>
       </c>
       <c r="P153" s="8">
-        <v>156.9</v>
+        <v>210.7</v>
       </c>
       <c r="Q153" s="10">
-        <v>63.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>40210</v>
+        <v>40238</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>17</v>
@@ -9302,39 +9310,39 @@
         <v>17</v>
       </c>
       <c r="H154" s="8">
-        <v>47.12</v>
-      </c>
-      <c r="I154" s="9">
-        <v>-7.29</v>
+        <v>52.57</v>
+      </c>
+      <c r="I154" s="10">
+        <v>11.6</v>
       </c>
       <c r="J154" s="10">
-        <v>57</v>
+        <v>35.9</v>
       </c>
       <c r="K154" s="8">
-        <v>97.94</v>
+        <v>150.5</v>
       </c>
       <c r="L154" s="10">
-        <v>83.6</v>
+        <v>63.5</v>
       </c>
       <c r="M154" s="8">
-        <v>48.69</v>
-      </c>
-      <c r="N154" s="9">
-        <v>-8.26</v>
+        <v>55.12</v>
+      </c>
+      <c r="N154" s="10">
+        <v>13.2</v>
       </c>
       <c r="O154" s="10">
-        <v>56.8</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="P154" s="8">
-        <v>101.8</v>
+        <v>156.9</v>
       </c>
       <c r="Q154" s="10">
-        <v>84.6</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
-        <v>40179</v>
+        <v>40210</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>17</v>
@@ -9355,39 +9363,39 @@
         <v>17</v>
       </c>
       <c r="H155" s="8">
-        <v>50.83</v>
+        <v>47.12</v>
       </c>
       <c r="I155" s="9">
-        <v>-4.87</v>
+        <v>-7.29</v>
       </c>
       <c r="J155" s="10">
-        <v>117.7</v>
+        <v>57</v>
       </c>
       <c r="K155" s="8">
-        <v>50.83</v>
+        <v>97.94</v>
       </c>
       <c r="L155" s="10">
-        <v>117.7</v>
+        <v>83.6</v>
       </c>
       <c r="M155" s="8">
-        <v>53.07</v>
-      </c>
-      <c r="N155" s="8" t="s">
-        <v>17</v>
+        <v>48.69</v>
+      </c>
+      <c r="N155" s="9">
+        <v>-8.26</v>
       </c>
       <c r="O155" s="10">
-        <v>120.3</v>
+        <v>56.8</v>
       </c>
       <c r="P155" s="8">
-        <v>53.07</v>
+        <v>101.8</v>
       </c>
       <c r="Q155" s="10">
-        <v>120.3</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
-        <v>40148</v>
+        <v>40179</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>17</v>
@@ -9408,39 +9416,39 @@
         <v>17</v>
       </c>
       <c r="H156" s="8">
-        <v>53.43</v>
+        <v>50.83</v>
       </c>
       <c r="I156" s="9">
-        <v>-2.52</v>
+        <v>-4.87</v>
       </c>
       <c r="J156" s="10">
-        <v>101.9</v>
+        <v>117.7</v>
       </c>
       <c r="K156" s="8">
-        <v>568.9</v>
-      </c>
-      <c r="L156" s="9">
-        <v>-5.93</v>
-      </c>
-      <c r="M156" s="8" t="s">
-        <v>17</v>
+        <v>50.83</v>
+      </c>
+      <c r="L156" s="10">
+        <v>117.7</v>
+      </c>
+      <c r="M156" s="8">
+        <v>53.07</v>
       </c>
       <c r="N156" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O156" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P156" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q156" s="8" t="s">
-        <v>17</v>
+      <c r="O156" s="10">
+        <v>120.3</v>
+      </c>
+      <c r="P156" s="8">
+        <v>53.07</v>
+      </c>
+      <c r="Q156" s="10">
+        <v>120.3</v>
       </c>
     </row>
     <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
-        <v>40118</v>
+        <v>40148</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>17</v>
@@ -9461,19 +9469,19 @@
         <v>17</v>
       </c>
       <c r="H157" s="8">
-        <v>54.82</v>
+        <v>53.43</v>
       </c>
       <c r="I157" s="9">
-        <v>-8.4600000000000009</v>
+        <v>-2.52</v>
       </c>
       <c r="J157" s="10">
-        <v>29.6</v>
+        <v>101.9</v>
       </c>
       <c r="K157" s="8">
-        <v>515.4</v>
+        <v>568.9</v>
       </c>
       <c r="L157" s="9">
-        <v>-10.9</v>
+        <v>-5.93</v>
       </c>
       <c r="M157" s="8" t="s">
         <v>17</v>
@@ -9493,7 +9501,7 @@
     </row>
     <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
-        <v>40087</v>
+        <v>40118</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>17</v>
@@ -9514,19 +9522,19 @@
         <v>17</v>
       </c>
       <c r="H158" s="8">
-        <v>59.89</v>
-      </c>
-      <c r="I158" s="10">
-        <v>0.17</v>
+        <v>54.82</v>
+      </c>
+      <c r="I158" s="9">
+        <v>-8.4600000000000009</v>
       </c>
       <c r="J158" s="10">
-        <v>7.47</v>
+        <v>29.6</v>
       </c>
       <c r="K158" s="8">
-        <v>460.6</v>
+        <v>515.4</v>
       </c>
       <c r="L158" s="9">
-        <v>-14.1</v>
+        <v>-10.9</v>
       </c>
       <c r="M158" s="8" t="s">
         <v>17</v>
@@ -9546,7 +9554,7 @@
     </row>
     <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
-        <v>40057</v>
+        <v>40087</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>17</v>
@@ -9567,19 +9575,19 @@
         <v>17</v>
       </c>
       <c r="H159" s="8">
-        <v>59.78</v>
+        <v>59.89</v>
       </c>
       <c r="I159" s="10">
-        <v>6.93</v>
+        <v>0.17</v>
       </c>
       <c r="J159" s="10">
-        <v>3.43</v>
+        <v>7.47</v>
       </c>
       <c r="K159" s="8">
-        <v>400.7</v>
+        <v>460.6</v>
       </c>
       <c r="L159" s="9">
-        <v>-16.600000000000001</v>
+        <v>-14.1</v>
       </c>
       <c r="M159" s="8" t="s">
         <v>17</v>
@@ -9599,7 +9607,7 @@
     </row>
     <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>40026</v>
+        <v>40057</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>17</v>
@@ -9620,19 +9628,19 @@
         <v>17</v>
       </c>
       <c r="H160" s="8">
-        <v>55.9</v>
+        <v>59.78</v>
       </c>
       <c r="I160" s="10">
-        <v>8.25</v>
-      </c>
-      <c r="J160" s="9">
-        <v>-5.0199999999999996</v>
+        <v>6.93</v>
+      </c>
+      <c r="J160" s="10">
+        <v>3.43</v>
       </c>
       <c r="K160" s="8">
-        <v>340.9</v>
+        <v>400.7</v>
       </c>
       <c r="L160" s="9">
-        <v>-19.3</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="M160" s="8" t="s">
         <v>17</v>
@@ -9652,7 +9660,7 @@
     </row>
     <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
-        <v>39995</v>
+        <v>40026</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>17</v>
@@ -9673,19 +9681,19 @@
         <v>17</v>
       </c>
       <c r="H161" s="8">
-        <v>51.64</v>
+        <v>55.9</v>
       </c>
       <c r="I161" s="10">
-        <v>1.1100000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="J161" s="9">
-        <v>-7.38</v>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="K161" s="8">
-        <v>285</v>
+        <v>340.9</v>
       </c>
       <c r="L161" s="9">
-        <v>-21.6</v>
+        <v>-19.3</v>
       </c>
       <c r="M161" s="8" t="s">
         <v>17</v>
@@ -9705,7 +9713,7 @@
     </row>
     <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
-        <v>39965</v>
+        <v>39995</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>17</v>
@@ -9726,19 +9734,19 @@
         <v>17</v>
       </c>
       <c r="H162" s="8">
-        <v>51.07</v>
+        <v>51.64</v>
       </c>
       <c r="I162" s="10">
-        <v>5.77</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="J162" s="9">
-        <v>-7.77</v>
+        <v>-7.38</v>
       </c>
       <c r="K162" s="8">
-        <v>233.4</v>
+        <v>285</v>
       </c>
       <c r="L162" s="9">
-        <v>-24.2</v>
+        <v>-21.6</v>
       </c>
       <c r="M162" s="8" t="s">
         <v>17</v>
@@ -9758,7 +9766,7 @@
     </row>
     <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
-        <v>39934</v>
+        <v>39965</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>17</v>
@@ -9779,19 +9787,19 @@
         <v>17</v>
       </c>
       <c r="H163" s="8">
-        <v>48.28</v>
+        <v>51.07</v>
       </c>
       <c r="I163" s="10">
-        <v>14.9</v>
+        <v>5.77</v>
       </c>
       <c r="J163" s="9">
-        <v>-9.66</v>
+        <v>-7.77</v>
       </c>
       <c r="K163" s="8">
-        <v>182.3</v>
+        <v>233.4</v>
       </c>
       <c r="L163" s="9">
-        <v>-27.8</v>
+        <v>-24.2</v>
       </c>
       <c r="M163" s="8" t="s">
         <v>17</v>
@@ -9811,7 +9819,7 @@
     </row>
     <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
-        <v>39904</v>
+        <v>39934</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>17</v>
@@ -9832,19 +9840,19 @@
         <v>17</v>
       </c>
       <c r="H164" s="8">
-        <v>42.01</v>
+        <v>48.28</v>
       </c>
       <c r="I164" s="10">
-        <v>8.6300000000000008</v>
+        <v>14.9</v>
       </c>
       <c r="J164" s="9">
-        <v>-15.5</v>
+        <v>-9.66</v>
       </c>
       <c r="K164" s="8">
-        <v>134</v>
+        <v>182.3</v>
       </c>
       <c r="L164" s="9">
-        <v>-32.6</v>
+        <v>-27.8</v>
       </c>
       <c r="M164" s="8" t="s">
         <v>17</v>
@@ -9864,7 +9872,7 @@
     </row>
     <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
-        <v>39873</v>
+        <v>39904</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>17</v>
@@ -9885,19 +9893,19 @@
         <v>17</v>
       </c>
       <c r="H165" s="8">
-        <v>38.68</v>
+        <v>42.01</v>
       </c>
       <c r="I165" s="10">
-        <v>28.9</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="J165" s="9">
-        <v>-25.9</v>
+        <v>-15.5</v>
       </c>
       <c r="K165" s="8">
-        <v>92.03</v>
+        <v>134</v>
       </c>
       <c r="L165" s="9">
-        <v>-38.4</v>
+        <v>-32.6</v>
       </c>
       <c r="M165" s="8" t="s">
         <v>17</v>
@@ -9917,7 +9925,7 @@
     </row>
     <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
-        <v>39845</v>
+        <v>39873</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>17</v>
@@ -9938,19 +9946,19 @@
         <v>17</v>
       </c>
       <c r="H166" s="8">
-        <v>30.01</v>
+        <v>38.68</v>
       </c>
       <c r="I166" s="10">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="J166" s="9">
-        <v>-34.6</v>
+        <v>-25.9</v>
       </c>
       <c r="K166" s="8">
-        <v>53.36</v>
+        <v>92.03</v>
       </c>
       <c r="L166" s="9">
-        <v>-45.1</v>
+        <v>-38.4</v>
       </c>
       <c r="M166" s="8" t="s">
         <v>17</v>
@@ -9970,7 +9978,7 @@
     </row>
     <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
-        <v>39814</v>
+        <v>39845</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>17</v>
@@ -9991,19 +9999,19 @@
         <v>17</v>
       </c>
       <c r="H167" s="8">
-        <v>23.35</v>
-      </c>
-      <c r="I167" s="9">
-        <v>-11.8</v>
+        <v>30.01</v>
+      </c>
+      <c r="I167" s="10">
+        <v>28.5</v>
       </c>
       <c r="J167" s="9">
-        <v>-54.4</v>
+        <v>-34.6</v>
       </c>
       <c r="K167" s="8">
-        <v>23.35</v>
+        <v>53.36</v>
       </c>
       <c r="L167" s="9">
-        <v>-54.4</v>
+        <v>-45.1</v>
       </c>
       <c r="M167" s="8" t="s">
         <v>17</v>
@@ -10023,7 +10031,7 @@
     </row>
     <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
-        <v>39783</v>
+        <v>39814</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>17</v>
@@ -10044,19 +10052,19 @@
         <v>17</v>
       </c>
       <c r="H168" s="8">
-        <v>26.47</v>
+        <v>23.35</v>
       </c>
       <c r="I168" s="9">
-        <v>-37.4</v>
+        <v>-11.8</v>
       </c>
       <c r="J168" s="9">
-        <v>-52.2</v>
+        <v>-54.4</v>
       </c>
       <c r="K168" s="8">
-        <v>604.70000000000005</v>
+        <v>23.35</v>
       </c>
       <c r="L168" s="9">
-        <v>-6.42</v>
+        <v>-54.4</v>
       </c>
       <c r="M168" s="8" t="s">
         <v>17</v>
@@ -10076,7 +10084,7 @@
     </row>
     <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
-        <v>39753</v>
+        <v>39783</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>17</v>
@@ -10097,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="H169" s="8">
-        <v>42.3</v>
+        <v>26.47</v>
       </c>
       <c r="I169" s="9">
-        <v>-24.1</v>
+        <v>-37.4</v>
       </c>
       <c r="J169" s="9">
-        <v>-28.3</v>
+        <v>-52.2</v>
       </c>
       <c r="K169" s="8">
-        <v>578.29999999999995</v>
+        <v>604.70000000000005</v>
       </c>
       <c r="L169" s="9">
-        <v>-2.13</v>
+        <v>-6.42</v>
       </c>
       <c r="M169" s="8" t="s">
         <v>17</v>
@@ -10129,7 +10137,7 @@
     </row>
     <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
-        <v>39722</v>
+        <v>39753</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>17</v>
@@ -10150,19 +10158,19 @@
         <v>17</v>
       </c>
       <c r="H170" s="8">
-        <v>55.72</v>
+        <v>42.3</v>
       </c>
       <c r="I170" s="9">
-        <v>-3.59</v>
+        <v>-24.1</v>
       </c>
       <c r="J170" s="9">
-        <v>-11.5</v>
+        <v>-28.3</v>
       </c>
       <c r="K170" s="8">
-        <v>536</v>
-      </c>
-      <c r="L170" s="10">
-        <v>0.77</v>
+        <v>578.29999999999995</v>
+      </c>
+      <c r="L170" s="9">
+        <v>-2.13</v>
       </c>
       <c r="M170" s="8" t="s">
         <v>17</v>
@@ -10182,7 +10190,7 @@
     </row>
     <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
-        <v>39692</v>
+        <v>39722</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>17</v>
@@ -10203,19 +10211,19 @@
         <v>17</v>
       </c>
       <c r="H171" s="8">
-        <v>57.8</v>
+        <v>55.72</v>
       </c>
       <c r="I171" s="9">
-        <v>-1.81</v>
+        <v>-3.59</v>
       </c>
       <c r="J171" s="9">
-        <v>-6.9</v>
+        <v>-11.5</v>
       </c>
       <c r="K171" s="8">
-        <v>480.3</v>
+        <v>536</v>
       </c>
       <c r="L171" s="10">
-        <v>2.41</v>
+        <v>0.77</v>
       </c>
       <c r="M171" s="8" t="s">
         <v>17</v>
@@ -10235,7 +10243,7 @@
     </row>
     <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
-        <v>39661</v>
+        <v>39692</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>17</v>
@@ -10256,19 +10264,19 @@
         <v>17</v>
       </c>
       <c r="H172" s="8">
-        <v>58.86</v>
-      </c>
-      <c r="I172" s="10">
-        <v>5.57</v>
+        <v>57.8</v>
+      </c>
+      <c r="I172" s="9">
+        <v>-1.81</v>
       </c>
       <c r="J172" s="9">
-        <v>-3.07</v>
+        <v>-6.9</v>
       </c>
       <c r="K172" s="8">
-        <v>422.5</v>
+        <v>480.3</v>
       </c>
       <c r="L172" s="10">
-        <v>3.83</v>
+        <v>2.41</v>
       </c>
       <c r="M172" s="8" t="s">
         <v>17</v>
@@ -10288,7 +10296,7 @@
     </row>
     <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
-        <v>39630</v>
+        <v>39661</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>17</v>
@@ -10309,19 +10317,19 @@
         <v>17</v>
       </c>
       <c r="H173" s="8">
-        <v>55.76</v>
+        <v>58.86</v>
       </c>
       <c r="I173" s="10">
-        <v>0.69</v>
+        <v>5.57</v>
       </c>
       <c r="J173" s="9">
-        <v>-0.94</v>
+        <v>-3.07</v>
       </c>
       <c r="K173" s="8">
-        <v>363.6</v>
+        <v>422.5</v>
       </c>
       <c r="L173" s="10">
-        <v>5.05</v>
+        <v>3.83</v>
       </c>
       <c r="M173" s="8" t="s">
         <v>17</v>
@@ -10341,7 +10349,7 @@
     </row>
     <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
-        <v>39600</v>
+        <v>39630</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>17</v>
@@ -10362,19 +10370,19 @@
         <v>17</v>
       </c>
       <c r="H174" s="8">
-        <v>55.37</v>
+        <v>55.76</v>
       </c>
       <c r="I174" s="10">
-        <v>3.61</v>
-      </c>
-      <c r="J174" s="10">
-        <v>5.71</v>
+        <v>0.69</v>
+      </c>
+      <c r="J174" s="9">
+        <v>-0.94</v>
       </c>
       <c r="K174" s="8">
-        <v>307.8</v>
+        <v>363.6</v>
       </c>
       <c r="L174" s="10">
-        <v>6.21</v>
+        <v>5.05</v>
       </c>
       <c r="M174" s="8" t="s">
         <v>17</v>
@@ -10394,7 +10402,7 @@
     </row>
     <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
-        <v>39569</v>
+        <v>39600</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>17</v>
@@ -10415,19 +10423,19 @@
         <v>17</v>
       </c>
       <c r="H175" s="8">
-        <v>53.45</v>
+        <v>55.37</v>
       </c>
       <c r="I175" s="10">
-        <v>7.54</v>
+        <v>3.61</v>
       </c>
       <c r="J175" s="10">
-        <v>3.78</v>
+        <v>5.71</v>
       </c>
       <c r="K175" s="8">
-        <v>252.5</v>
+        <v>307.8</v>
       </c>
       <c r="L175" s="10">
-        <v>6.32</v>
+        <v>6.21</v>
       </c>
       <c r="M175" s="8" t="s">
         <v>17</v>
@@ -10447,7 +10455,7 @@
     </row>
     <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
-        <v>39539</v>
+        <v>39569</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>17</v>
@@ -10468,19 +10476,19 @@
         <v>17</v>
       </c>
       <c r="H176" s="8">
-        <v>49.7</v>
-      </c>
-      <c r="I176" s="9">
-        <v>-4.8</v>
+        <v>53.45</v>
+      </c>
+      <c r="I176" s="10">
+        <v>7.54</v>
       </c>
       <c r="J176" s="10">
-        <v>2.59</v>
+        <v>3.78</v>
       </c>
       <c r="K176" s="8">
-        <v>199</v>
+        <v>252.5</v>
       </c>
       <c r="L176" s="10">
-        <v>7.02</v>
+        <v>6.32</v>
       </c>
       <c r="M176" s="8" t="s">
         <v>17</v>
@@ -10500,7 +10508,7 @@
     </row>
     <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
-        <v>39508</v>
+        <v>39539</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>17</v>
@@ -10521,19 +10529,19 @@
         <v>17</v>
       </c>
       <c r="H177" s="8">
-        <v>52.21</v>
-      </c>
-      <c r="I177" s="10">
-        <v>13.7</v>
+        <v>49.7</v>
+      </c>
+      <c r="I177" s="9">
+        <v>-4.8</v>
       </c>
       <c r="J177" s="10">
-        <v>6.97</v>
+        <v>2.59</v>
       </c>
       <c r="K177" s="8">
-        <v>149.30000000000001</v>
+        <v>199</v>
       </c>
       <c r="L177" s="10">
-        <v>8.58</v>
+        <v>7.02</v>
       </c>
       <c r="M177" s="8" t="s">
         <v>17</v>
@@ -10553,7 +10561,7 @@
     </row>
     <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
-        <v>39479</v>
+        <v>39508</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>17</v>
@@ -10574,19 +10582,19 @@
         <v>17</v>
       </c>
       <c r="H178" s="8">
-        <v>45.91</v>
-      </c>
-      <c r="I178" s="9">
-        <v>-10.3</v>
+        <v>52.21</v>
+      </c>
+      <c r="I178" s="10">
+        <v>13.7</v>
       </c>
       <c r="J178" s="10">
-        <v>8.06</v>
+        <v>6.97</v>
       </c>
       <c r="K178" s="8">
-        <v>97.11</v>
+        <v>149.30000000000001</v>
       </c>
       <c r="L178" s="10">
-        <v>9.4700000000000006</v>
+        <v>8.58</v>
       </c>
       <c r="M178" s="8" t="s">
         <v>17</v>
@@ -10606,7 +10614,7 @@
     </row>
     <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>39448</v>
+        <v>39479</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>17</v>
@@ -10627,19 +10635,19 @@
         <v>17</v>
       </c>
       <c r="H179" s="8">
-        <v>51.19</v>
+        <v>45.91</v>
       </c>
       <c r="I179" s="9">
-        <v>-7.5</v>
+        <v>-10.3</v>
       </c>
       <c r="J179" s="10">
-        <v>10.8</v>
+        <v>8.06</v>
       </c>
       <c r="K179" s="8">
-        <v>51.19</v>
+        <v>97.11</v>
       </c>
       <c r="L179" s="10">
-        <v>10.8</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="M179" s="8" t="s">
         <v>17</v>
@@ -10659,7 +10667,7 @@
     </row>
     <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
-        <v>39417</v>
+        <v>39448</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>17</v>
@@ -10680,19 +10688,19 @@
         <v>17</v>
       </c>
       <c r="H180" s="8">
-        <v>55.35</v>
+        <v>51.19</v>
       </c>
       <c r="I180" s="9">
-        <v>-6.21</v>
-      </c>
-      <c r="J180" s="8" t="s">
-        <v>17</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J180" s="10">
+        <v>10.8</v>
       </c>
       <c r="K180" s="8">
-        <v>646.20000000000005</v>
-      </c>
-      <c r="L180" s="8" t="s">
-        <v>17</v>
+        <v>51.19</v>
+      </c>
+      <c r="L180" s="10">
+        <v>10.8</v>
       </c>
       <c r="M180" s="8" t="s">
         <v>17</v>
@@ -10712,7 +10720,7 @@
     </row>
     <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
-        <v>39387</v>
+        <v>39417</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>17</v>
@@ -10733,16 +10741,16 @@
         <v>17</v>
       </c>
       <c r="H181" s="8">
-        <v>59.01</v>
+        <v>55.35</v>
       </c>
       <c r="I181" s="9">
-        <v>-6.23</v>
+        <v>-6.21</v>
       </c>
       <c r="J181" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K181" s="8">
-        <v>590.9</v>
+        <v>646.20000000000005</v>
       </c>
       <c r="L181" s="8" t="s">
         <v>17</v>
@@ -10765,7 +10773,7 @@
     </row>
     <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
-        <v>39356</v>
+        <v>39387</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>17</v>
@@ -10786,16 +10794,16 @@
         <v>17</v>
       </c>
       <c r="H182" s="8">
-        <v>62.93</v>
-      </c>
-      <c r="I182" s="10">
-        <v>1.37</v>
+        <v>59.01</v>
+      </c>
+      <c r="I182" s="9">
+        <v>-6.23</v>
       </c>
       <c r="J182" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K182" s="8">
-        <v>531.9</v>
+        <v>590.9</v>
       </c>
       <c r="L182" s="8" t="s">
         <v>17</v>
@@ -10818,7 +10826,7 @@
     </row>
     <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
-        <v>39326</v>
+        <v>39356</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>17</v>
@@ -10839,16 +10847,16 @@
         <v>17</v>
       </c>
       <c r="H183" s="8">
-        <v>62.08</v>
+        <v>62.93</v>
       </c>
       <c r="I183" s="10">
-        <v>2.23</v>
+        <v>1.37</v>
       </c>
       <c r="J183" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K183" s="8">
-        <v>468.9</v>
+        <v>531.9</v>
       </c>
       <c r="L183" s="8" t="s">
         <v>17</v>
@@ -10871,7 +10879,7 @@
     </row>
     <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
-        <v>39295</v>
+        <v>39326</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>17</v>
@@ -10892,16 +10900,16 @@
         <v>17</v>
       </c>
       <c r="H184" s="8">
-        <v>60.72</v>
+        <v>62.08</v>
       </c>
       <c r="I184" s="10">
-        <v>7.88</v>
+        <v>2.23</v>
       </c>
       <c r="J184" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K184" s="8">
-        <v>406.9</v>
+        <v>468.9</v>
       </c>
       <c r="L184" s="8" t="s">
         <v>17</v>
@@ -10924,7 +10932,7 @@
     </row>
     <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
-        <v>39264</v>
+        <v>39295</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>17</v>
@@ -10945,16 +10953,16 @@
         <v>17</v>
       </c>
       <c r="H185" s="8">
-        <v>56.29</v>
+        <v>60.72</v>
       </c>
       <c r="I185" s="10">
-        <v>7.45</v>
+        <v>7.88</v>
       </c>
       <c r="J185" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K185" s="8">
-        <v>346.1</v>
+        <v>406.9</v>
       </c>
       <c r="L185" s="8" t="s">
         <v>17</v>
@@ -10977,7 +10985,7 @@
     </row>
     <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
-        <v>39234</v>
+        <v>39264</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>17</v>
@@ -10998,16 +11006,16 @@
         <v>17</v>
       </c>
       <c r="H186" s="8">
-        <v>52.39</v>
+        <v>56.29</v>
       </c>
       <c r="I186" s="10">
-        <v>1.72</v>
+        <v>7.45</v>
       </c>
       <c r="J186" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K186" s="8">
-        <v>289.8</v>
+        <v>346.1</v>
       </c>
       <c r="L186" s="8" t="s">
         <v>17</v>
@@ -11030,7 +11038,7 @@
     </row>
     <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
-        <v>39203</v>
+        <v>39234</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>17</v>
@@ -11051,16 +11059,16 @@
         <v>17</v>
       </c>
       <c r="H187" s="8">
-        <v>51.5</v>
+        <v>52.39</v>
       </c>
       <c r="I187" s="10">
-        <v>6.3</v>
+        <v>1.72</v>
       </c>
       <c r="J187" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K187" s="8">
-        <v>237.5</v>
+        <v>289.8</v>
       </c>
       <c r="L187" s="8" t="s">
         <v>17</v>
@@ -11083,7 +11091,7 @@
     </row>
     <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
-        <v>39173</v>
+        <v>39203</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>17</v>
@@ -11104,16 +11112,16 @@
         <v>17</v>
       </c>
       <c r="H188" s="8">
-        <v>48.45</v>
-      </c>
-      <c r="I188" s="9">
-        <v>-0.73</v>
+        <v>51.5</v>
+      </c>
+      <c r="I188" s="10">
+        <v>6.3</v>
       </c>
       <c r="J188" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K188" s="8">
-        <v>186</v>
+        <v>237.5</v>
       </c>
       <c r="L188" s="8" t="s">
         <v>17</v>
@@ -11136,7 +11144,7 @@
     </row>
     <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
-        <v>39142</v>
+        <v>39173</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>17</v>
@@ -11157,16 +11165,16 @@
         <v>17</v>
       </c>
       <c r="H189" s="8">
-        <v>48.8</v>
-      </c>
-      <c r="I189" s="10">
-        <v>14.9</v>
+        <v>48.45</v>
+      </c>
+      <c r="I189" s="9">
+        <v>-0.73</v>
       </c>
       <c r="J189" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K189" s="8">
-        <v>137.5</v>
+        <v>186</v>
       </c>
       <c r="L189" s="8" t="s">
         <v>17</v>
@@ -11189,7 +11197,7 @@
     </row>
     <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
-        <v>39114</v>
+        <v>39142</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>17</v>
@@ -11210,16 +11218,16 @@
         <v>17</v>
       </c>
       <c r="H190" s="8">
-        <v>42.49</v>
-      </c>
-      <c r="I190" s="9">
-        <v>-8.06</v>
+        <v>48.8</v>
+      </c>
+      <c r="I190" s="10">
+        <v>14.9</v>
       </c>
       <c r="J190" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K190" s="8">
-        <v>88.71</v>
+        <v>137.5</v>
       </c>
       <c r="L190" s="8" t="s">
         <v>17</v>
@@ -11242,54 +11250,107 @@
     </row>
     <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
+        <v>39114</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H191" s="8">
+        <v>42.49</v>
+      </c>
+      <c r="I191" s="9">
+        <v>-8.06</v>
+      </c>
+      <c r="J191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K191" s="8">
+        <v>88.71</v>
+      </c>
+      <c r="L191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P191" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q191" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
         <v>39083</v>
       </c>
-      <c r="B191" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E191" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H191" s="8">
+      <c r="B192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H192" s="8">
         <v>46.22</v>
       </c>
-      <c r="I191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K191" s="8">
+      <c r="I192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K192" s="8">
         <v>46.22</v>
       </c>
-      <c r="L191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q191" s="8" t="s">
+      <c r="L192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P192" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q192" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11308,7 +11369,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>